--- a/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>AME</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1730900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1622800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1646100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1597100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1625700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1551800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1514600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1458500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1503700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1440700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1386300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1215700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1198900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1126900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1011900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1202200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1304800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1276600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1289400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1287700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1271300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1193000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1208900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1172600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1143100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1084800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1064600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1007700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>973000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1115900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1020900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1053200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1022500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1063700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1004600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>988200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>948800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>982400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>949400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>912700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>789400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>770000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>732700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>669200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>780900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>858200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>823300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>838200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>851300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>835300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>783000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>791200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>776800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>767000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>722100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>702200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>667400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>735600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>612700</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>615100</v>
+      </c>
+      <c r="E10" s="3">
         <v>601900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>592900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>574600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>562000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>547200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>526400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>509700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>521300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>491300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>473600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>426300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>428900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>394200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>342700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>421300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>446600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>453300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>451200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>436400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>436000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>410000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>417700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>395800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>376100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>362700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>362400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>340300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>237400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>332300</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1311,8 +1330,8 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1320,20 +1339,20 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>-97100</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1350,8 +1369,8 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1374,8 +1393,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1442,8 +1464,8 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>8</v>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>8</v>
@@ -1463,11 +1485,14 @@
       <c r="AE15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AF15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG15" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1285900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1184700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1227300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1191600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1227600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1167300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1149700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1105300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1142600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1103100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1069700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>922400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>900800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>856200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>784900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>829200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1007200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>975600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>994000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1004400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>989300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>927700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>938800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>914500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>913500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>854800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>835100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>790200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>799700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>743900</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>445000</v>
+      </c>
+      <c r="E18" s="3">
         <v>438100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>418800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>405500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>398100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>384500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>364900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>353200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>361100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>337600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>316600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>293300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>298100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>270700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>227000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>373000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>297600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>301000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>295400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>283300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>282000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>265300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>270100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>258100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>229600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>230000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>229500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>217500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>173300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>201100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1747,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-6200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4400</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-1900</v>
       </c>
       <c r="O20" s="3">
         <v>-1900</v>
       </c>
       <c r="P20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2900</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-1000</v>
       </c>
       <c r="Y20" s="3">
         <v>-1000</v>
       </c>
       <c r="Z20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>533000</v>
+      </c>
+      <c r="E21" s="3">
         <v>513700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>496700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>482500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>490000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>463500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>443900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>433900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>437400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>414800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>387400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>356000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>361000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>332300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>290500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>439900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>355100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>350800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>349200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>337100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>332700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>312500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>317900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>306300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>274000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>273800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>271800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>258500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>225600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E22" s="3">
         <v>18400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>18700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>20600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>23000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>20200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>20400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>19600</v>
-      </c>
-      <c r="K22" s="3">
-        <v>20500</v>
       </c>
       <c r="L22" s="3">
         <v>20500</v>
       </c>
       <c r="M22" s="3">
+        <v>20500</v>
+      </c>
+      <c r="N22" s="3">
         <v>20400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>18900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>19500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>21200</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>22700</v>
       </c>
       <c r="R22" s="3">
         <v>22700</v>
       </c>
       <c r="S22" s="3">
+        <v>22700</v>
+      </c>
+      <c r="T22" s="3">
         <v>23000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>21300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>21500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>22700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>20300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>19400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>20800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>21700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>24300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>24700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>24600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>24500</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>23600</v>
       </c>
       <c r="AF22" s="3">
         <v>23600</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>23600</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>416900</v>
+      </c>
+      <c r="E23" s="3">
         <v>413500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>396400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>379600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>378500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>367500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>346500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>336200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>339300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>319700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>291800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>272500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>276700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>248100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>206500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>351100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>268000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>274200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>270600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>256900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>258800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>244900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>248200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>235800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>197500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>204400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>203400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>191400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>145300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>74100</v>
+      </c>
+      <c r="E24" s="3">
         <v>73100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>72100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>73900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>71400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>69900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>64100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>63800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>57600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>62200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>60100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>53200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>55700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>43500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>40200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>70500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>47200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>53500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>55100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>52700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>59100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>53700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>54400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>54500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>50600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>50900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>52900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>52500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>36100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>342900</v>
+      </c>
+      <c r="E26" s="3">
         <v>340400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>324200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>305700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>307100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>297600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>282400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>272400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>281700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>257500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>231700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>219200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>221000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>204600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>166200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>280600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>220800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>220700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>215500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>204300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>199700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>191200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>193900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>181300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>146900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>153500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>150500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>138900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>109100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>342900</v>
+      </c>
+      <c r="E27" s="3">
         <v>340400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>324200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>305700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>307100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>297600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>282400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>272400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>281700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>257500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>231700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>219200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>221000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>204600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>166200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>280600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>220800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>220700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>215500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>204300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>199700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>191200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>193900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>181300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>146900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>153500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>150500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>138900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>109100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2587,8 +2647,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2605,11 +2665,11 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>11800</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2617,11 +2677,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>91600</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E32" s="3">
         <v>6200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4400</v>
-      </c>
-      <c r="N32" s="3">
-        <v>1900</v>
       </c>
       <c r="O32" s="3">
         <v>1900</v>
       </c>
       <c r="P32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2900</v>
-      </c>
-      <c r="X32" s="3">
-        <v>1000</v>
       </c>
       <c r="Y32" s="3">
         <v>1000</v>
       </c>
       <c r="Z32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA32" s="3">
         <v>600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>7800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>4400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>342900</v>
+      </c>
+      <c r="E33" s="3">
         <v>340400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>324200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>305700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>307100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>297600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>282400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>272400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>281700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>257500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>231700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>219200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>221000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>204600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>166200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>280600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>220800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>220700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>215500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>204300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>211500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>191200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>193900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>181300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>238500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>153500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>150500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>138900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>109100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>342900</v>
+      </c>
+      <c r="E35" s="3">
         <v>340400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>324200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>305700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>307100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>297600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>282400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>272400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>281700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>257500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>231700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>219200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>221000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>204600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>166200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>280600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>220800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>220700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>215500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>204300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>211500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>191200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>193900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>181300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>238500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>153500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>150500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>138900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>109100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>409800</v>
+      </c>
+      <c r="E41" s="3">
         <v>841900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>605600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>399900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>345400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>309900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>348700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>340300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>346800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>358700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>390600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1123700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1212800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1304800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1131000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1253400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>393000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>735400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>567900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>368100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>354000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>518700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>557700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>556800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>646300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>736400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>516500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>570200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>717300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>445500</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,652 +3625,676 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1153800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1076600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1074400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1028900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1039100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>988100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>993000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>957200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>924500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>851400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>827900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>749900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>666400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>682900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>688000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>793000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>817800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>840000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>839600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>839500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>732800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>714900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>711000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>684600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>668200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>640800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>642300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>603900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>592300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>595100</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1132500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1087600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1107800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1117100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1044300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1025100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>966600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>866500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>769200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>738700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>711600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>604300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>559200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>584800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>621500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>654300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>624600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>623700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>634100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>640600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>624700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>620100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>614400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>596300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>540500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>546900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>541200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>529900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>492100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>537200</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>128600</v>
+      </c>
+      <c r="E45" s="3">
         <v>112600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>111800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>120100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>99300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>109300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>103400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>108900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>88300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>113100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>111900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>95600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>84000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>70500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>76700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>73800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>190400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>73200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>85500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>76500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>124600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>144800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>135100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>122500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>79700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>100400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>89300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>83400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>126500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>119100</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2824700</v>
+      </c>
+      <c r="E46" s="3">
         <v>3118700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2899600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2665900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2528100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2432600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2411600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2272800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2128800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2061800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2042100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2573500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2522500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2643000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2517100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2774500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2025800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2272200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2127200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1924600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1836100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1998600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2018100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1960200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1934700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2024500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1789300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1787400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1928200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1696900</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>464900</v>
+      </c>
+      <c r="E47" s="3">
         <v>414700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>402300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>393800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>382500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>405800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>399500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>387600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>375000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>325500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>322200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>297200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>292600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>281800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>289800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>280300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>279800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>257300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>269600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>262200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>256200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>256800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>244800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>240500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>239100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>159100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>155000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>152400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>146300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>175100</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1121000</v>
+      </c>
+      <c r="E48" s="3">
         <v>797100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>809200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>804700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>805900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>756100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>766000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>780300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>787100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>766600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>777500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>716000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>693800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>675400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>680800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>703300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>728600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>711600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>721200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>724900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>554100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>487400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>490100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>492400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>493300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>495000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>492500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>482900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>473200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>478600</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10612900</v>
+      </c>
+      <c r="E49" s="3">
         <v>8762900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8728900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8751600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8714600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8444400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8407900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8531300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8607400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8525900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8613500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6993300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6848600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6833200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6823500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6843800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6810400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5978600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5951700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5979800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6015800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5365200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5399400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5365300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5129000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5104700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5098200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4876000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4553000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4626400</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4480,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4456,8 +4575,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15023500</v>
+      </c>
+      <c r="E54" s="3">
         <v>13093400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12839900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12616000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12431100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12038900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11985000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11972000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11898200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11679700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11755300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10579900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10357500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10433400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10311200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10601900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9844600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9219700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9069600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8891500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8662300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8108000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8152500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8058400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7796100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7783300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7535000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7298800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7100700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6977100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4837,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>516600</v>
+      </c>
+      <c r="E57" s="3">
         <v>486600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>487700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>526100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>497100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>524300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>540700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>504200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>470300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>446400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>446500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>397100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>360400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>324800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>337500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>373900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>377200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>381900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>390400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>405600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>399600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>389100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>394300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>382300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>437300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>409400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>405900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>382800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>369500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>345500</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1417900</v>
+      </c>
+      <c r="E58" s="3">
         <v>304500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>70000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>226100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>272000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>354800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>331400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>315100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>415700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>700000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>94700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>132300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>505000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>115900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>510800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>497400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>199500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>98400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>104200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>358900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>68700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>307700</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>308100</v>
       </c>
       <c r="AA58" s="3">
         <v>308100</v>
       </c>
       <c r="AB58" s="3">
+        <v>308100</v>
+      </c>
+      <c r="AC58" s="3">
         <v>509600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>272600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>338000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>278900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>613700</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>948100</v>
+      </c>
+      <c r="E59" s="3">
         <v>882700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>848100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>856600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>841000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>795100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>737600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>755100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>778000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>771800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>711100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>646700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>583300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>573600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>564100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>593000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>551200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>529000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>489800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>497400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>500300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>512000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>480600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>469500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>393200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>351400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>316700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>296000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>276000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>257600</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2882600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1673700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1341200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1452700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1564200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1591400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1633000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1590700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1563300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1633800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1857600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1138500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1075900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1403500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1017500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1477700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1425900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1110500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>978600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1007200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1258700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>969900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1182500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1159900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1138700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1270300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>995100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1016800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>924400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1216700</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1895400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1856100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2186300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2175900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2158900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2085400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2147400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2204600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2229100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2238900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2262100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2256900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2281400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2295800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2753300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2741800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2271300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2229300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2368700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2368200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2273800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1832500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1838200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1897600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1866200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1920900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2128800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2076600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2062600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1515300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1221000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1231000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1230400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1231500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1229500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1254500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1245000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1233800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1248600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1292200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1063800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1050800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1029900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1054000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1056500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1031900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1014000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1055600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1059400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>887800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>793700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>793600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>796400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>763600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>825900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>818800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>801200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>857100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>846400</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6293300</v>
+      </c>
+      <c r="E66" s="3">
         <v>4750900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4758500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4858900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4954600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4906300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5034900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5040300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5026300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5121300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5412000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4459100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4408100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4729200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4824700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5275900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4729100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4353700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4402800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4434900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4420400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3596100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3814400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3854000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3768400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4017100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3942800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3894600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3844200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3603900</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9940300</v>
+      </c>
+      <c r="E72" s="3">
         <v>9655100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9372400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9105700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8857500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8600900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8353700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8121800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7900100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7664700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7453400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7267900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7094700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6915000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6751700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6626700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6387600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6198800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6010000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5826300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5653800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5474100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5315200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5153700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5002400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4784600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4651800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4522000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4403700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4315100</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8730200</v>
+      </c>
+      <c r="E76" s="3">
         <v>8342500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8081400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7757100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7476500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7132700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6950100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6931700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6871900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6558400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6343300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6120700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5949300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5704200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5486400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5326000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5115500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4866000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4666800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4456600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4241900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4511900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4338100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4204400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4027600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3766200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3592200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3404200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3256500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3373200</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>342900</v>
+      </c>
+      <c r="E81" s="3">
         <v>340400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>324200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>305700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>307100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>297600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>282400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>272400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>281700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>257500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>231700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>219200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>221000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>204600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>166200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>280600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>220800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>220700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>215500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>204300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>211500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>191200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>193900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>181300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>238500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>153500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>150500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>138900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>109100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>91900</v>
+      </c>
+      <c r="E83" s="3">
         <v>81800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>81600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>82400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>88500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>75800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>77100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>78100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>77600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>74700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>75200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>64600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>64900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>63000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>61300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>66100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>64100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>55300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>57200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>57500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>53600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>48100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>48900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>48800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>52200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>44600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>43800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>42500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>56700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>540700</v>
+      </c>
+      <c r="E89" s="3">
         <v>472900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>335200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>386500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>385000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>327100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>235900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>201300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>281900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>307100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>287000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>284400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>385900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>309700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>314600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>270800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>342200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>329600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>246300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>196300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>296200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>248800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>203100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>177400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>252900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>239000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>199000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>142400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>247300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>169000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-59700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-28700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-27800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-58200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-28300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-26200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-26400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-43400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-23500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-37000</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-10100</v>
       </c>
       <c r="Q91" s="3">
         <v>-10100</v>
       </c>
       <c r="R91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="S91" s="3">
         <v>-16900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-40800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-18200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-21900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-21400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-34600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-18900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-16300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-12300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-29400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-13400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2050100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-176300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-27800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-122200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-297200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-214500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-26200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-160700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1597600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-284500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-37100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>115600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-977600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-133700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-21900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-17800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-785800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-22500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-148200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-253600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-63400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-15700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-198400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-348300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-52400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-81800</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7897,70 +8130,70 @@
         <v>-57600</v>
       </c>
       <c r="F96" s="3">
+        <v>-57600</v>
+      </c>
+      <c r="G96" s="3">
         <v>-57500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-50500</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-50400</v>
       </c>
       <c r="I96" s="3">
         <v>-50400</v>
       </c>
       <c r="J96" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="K96" s="3">
         <v>-50800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-46300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-46200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-46100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-46000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-41300</v>
       </c>
       <c r="P96" s="3">
         <v>-41300</v>
       </c>
       <c r="Q96" s="3">
-        <v>-41200</v>
+        <v>-41300</v>
       </c>
       <c r="R96" s="3">
         <v>-41200</v>
       </c>
       <c r="S96" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="T96" s="3">
         <v>-32000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-31800</v>
       </c>
       <c r="V96" s="3">
         <v>-31800</v>
       </c>
       <c r="W96" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="X96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-32400</v>
       </c>
       <c r="Y96" s="3">
         <v>-32400</v>
       </c>
       <c r="Z96" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-32300</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-20700</v>
       </c>
       <c r="AB96" s="3">
         <v>-20700</v>
@@ -7969,16 +8202,19 @@
         <v>-20700</v>
       </c>
       <c r="AD96" s="3">
-        <v>-20600</v>
+        <v>-20700</v>
       </c>
       <c r="AE96" s="3">
         <v>-20600</v>
       </c>
       <c r="AF96" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-20700</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1062100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-47700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-102100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-215000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-74500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-130800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-183000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-187400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-131900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-320400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>575600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-84000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-454700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-141100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-430300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>486600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>280800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-16400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-25700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-165900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>330300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-261700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-28500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-27100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-286200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-75100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>51900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>98400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-97900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-12500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>22200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-20500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-18400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>13900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>11300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-12600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>12200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-12000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-5400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-25600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>13700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>6600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>16500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>20800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>6900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-21600</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-432100</v>
+      </c>
+      <c r="E102" s="3">
         <v>236300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>205700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>54500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>35400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-38700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-32000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-733000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-89200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-92000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>173900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-122400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>860400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-342300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>167500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>199800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>14100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-164700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-39000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-89500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-90100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>219900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-53800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-147000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>271800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-10700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>AME</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1736200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1730900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1622800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1646100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1597100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1625700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1551800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1514600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1458500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1503700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1440700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1386300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1215700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1198900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1126900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1011900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1202200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1304800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1276600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1289400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1287700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1271300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1193000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1208900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1172600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1143100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1084800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1064600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1007700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>973000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1115500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1115900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1020900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1053200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1022500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1063700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1004600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>988200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>948800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>982400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>949400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>912700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>789400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>770000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>732700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>669200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>780900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>858200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>823300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>838200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>851300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>835300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>783000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>791200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>776800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>767000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>722100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>702200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>667400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>735600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>612700</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>620700</v>
+      </c>
+      <c r="E10" s="3">
         <v>615100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>601900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>592900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>574600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>562000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>547200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>526400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>509700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>521300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>491300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>473600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>426300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>428900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>394200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>342700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>421300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>446600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>453300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>451200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>436400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>436000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>410000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>417700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>395800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>376100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>362700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>362400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>340300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>237400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>332300</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,31 +1318,34 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>29200</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1333,8 +1353,8 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1342,20 +1362,20 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>-97100</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1372,8 +1392,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1396,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1467,8 +1490,8 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>8</v>
+      <c r="Z15" s="3">
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>8</v>
@@ -1488,11 +1511,14 @@
       <c r="AF15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AG15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH15" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1319000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1285900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1184700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1227300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1191600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1227600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1167300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1149700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1105300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1142600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1103100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1069700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>922400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>900800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>856200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>784900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>829200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1007200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>975600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>994000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1004400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>989300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>927700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>938800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>914500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>913500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>854800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>835100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>790200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>799700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>743900</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>417200</v>
+      </c>
+      <c r="E18" s="3">
         <v>445000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>438100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>418800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>405500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>398100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>384500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>364900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>353200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>361100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>337600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>316600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>293300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>298100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>270700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>227000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>373000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>297600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>301000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>295400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>283300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>282000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>265300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>270100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>258100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>229600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>230000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>229500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>217500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>173300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>201100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,483 +1781,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4400</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-1900</v>
       </c>
       <c r="P20" s="3">
         <v>-1900</v>
       </c>
       <c r="Q20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-1000</v>
       </c>
       <c r="Z20" s="3">
         <v>-1000</v>
       </c>
       <c r="AA20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>514600</v>
+      </c>
+      <c r="E21" s="3">
         <v>533000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>513700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>496700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>482500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>490000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>463500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>443900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>433900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>437400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>414800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>387400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>356000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>361000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>332300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>290500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>439900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>355100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>350800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>349200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>337100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>332700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>312500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>317900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>306300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>274000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>273800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>271800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>258500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>225600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E22" s="3">
         <v>24100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>18400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>18700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>20600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>23000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>20200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>19600</v>
-      </c>
-      <c r="L22" s="3">
-        <v>20500</v>
       </c>
       <c r="M22" s="3">
         <v>20500</v>
       </c>
       <c r="N22" s="3">
+        <v>20500</v>
+      </c>
+      <c r="O22" s="3">
         <v>20400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>18900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>19500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>21200</v>
-      </c>
-      <c r="R22" s="3">
-        <v>22700</v>
       </c>
       <c r="S22" s="3">
         <v>22700</v>
       </c>
       <c r="T22" s="3">
+        <v>22700</v>
+      </c>
+      <c r="U22" s="3">
         <v>23000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>21300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>21500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>22700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>20300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>19400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>20800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>21700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>24300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>24700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>24600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>24500</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>23600</v>
       </c>
       <c r="AG22" s="3">
         <v>23600</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>23600</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>381300</v>
+      </c>
+      <c r="E23" s="3">
         <v>416900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>413500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>396400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>379600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>378500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>367500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>346500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>336200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>339300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>319700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>291800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>272500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>276700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>248100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>206500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>351100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>268000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>274200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>270600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>256900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>258800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>244900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>248200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>235800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>197500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>204400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>203400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>191400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>145300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E24" s="3">
         <v>74100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>73100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>72100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>73900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>71400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>69900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>64100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>63800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>57600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>62200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>60100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>53200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>55700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>43500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>40200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>70500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>47200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>53500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>55100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>52700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>59100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>53700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>54400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>54500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>50600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>50900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>52900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>52500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>36100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>310900</v>
+      </c>
+      <c r="E26" s="3">
         <v>342900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>340400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>324200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>305700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>307100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>297600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>282400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>272400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>281700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>257500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>231700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>219200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>221000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>204600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>166200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>280600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>220800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>220700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>215500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>204300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>199700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>191200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>193900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>181300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>146900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>153500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>150500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>138900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>109100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>310900</v>
+      </c>
+      <c r="E27" s="3">
         <v>342900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>340400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>324200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>305700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>307100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>297600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>282400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>272400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>281700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>257500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>231700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>219200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>221000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>204600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>166200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>280600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>220800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>220700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>215500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>204300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>199700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>191200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>193900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>181300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>146900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>153500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>150500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>138900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>109100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2650,8 +2711,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2668,11 +2729,11 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>11800</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2680,11 +2741,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>91600</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>700</v>
+      </c>
+      <c r="E32" s="3">
         <v>4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4400</v>
-      </c>
-      <c r="O32" s="3">
-        <v>1900</v>
       </c>
       <c r="P32" s="3">
         <v>1900</v>
       </c>
       <c r="Q32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R32" s="3">
         <v>1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2900</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>1000</v>
       </c>
       <c r="Z32" s="3">
         <v>1000</v>
       </c>
       <c r="AA32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB32" s="3">
         <v>600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>7800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>4400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>310900</v>
+      </c>
+      <c r="E33" s="3">
         <v>342900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>340400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>324200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>305700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>307100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>297600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>282400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>272400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>281700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>257500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>231700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>219200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>221000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>204600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>166200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>280600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>220800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>220700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>215500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>204300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>211500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>191200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>193900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>181300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>238500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>153500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>150500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>138900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>109100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>310900</v>
+      </c>
+      <c r="E35" s="3">
         <v>342900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>340400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>324200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>305700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>307100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>297600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>282400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>272400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>281700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>257500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>231700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>219200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>221000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>204600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>166200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>280600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>220800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>220700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>215500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>204300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>211500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>191200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>193900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>181300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>238500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>153500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>150500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>138900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>109100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>373800</v>
+      </c>
+      <c r="E41" s="3">
         <v>409800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>841900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>605600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>399900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>345400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>309900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>348700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>340300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>346800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>358700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>390600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1123700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1212800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1304800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1131000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1253400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>393000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>735400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>567900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>368100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>354000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>518700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>557700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>556800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>646300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>736400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>516500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>570200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>717300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>445500</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,673 +3718,697 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1130800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1153800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1076600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1074400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1028900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1039100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>988100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>993000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>957200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>924500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>851400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>827900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>749900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>666400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>682900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>688000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>793000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>817800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>840000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>839600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>839500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>732800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>714900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>711000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>684600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>668200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>640800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>642300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>603900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>592300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>595100</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1127300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1132500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1087600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1107800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1117100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1044300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1025100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>966600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>866500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>769200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>738700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>711600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>604300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>559200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>584800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>621500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>654300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>624600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>623700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>634100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>640600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>624700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>620100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>614400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>596300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>540500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>546900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>541200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>529900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>492100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>537200</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>143600</v>
+      </c>
+      <c r="E45" s="3">
         <v>128600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>112600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>111800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>120100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>99300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>109300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>103400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>108900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>88300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>113100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>111900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>95600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>84000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>70500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>76700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>73800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>190400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>73200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>85500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>76500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>124600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>144800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>135100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>122500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>79700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>100400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>89300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>83400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>126500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>119100</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2775500</v>
+      </c>
+      <c r="E46" s="3">
         <v>2824700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3118700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2899600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2665900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2528100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2432600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2411600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2272800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2128800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2061800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2042100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2573500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2522500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2643000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2517100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2774500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2025800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2272200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2127200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1924600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1836100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1998600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2018100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1960200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1934700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2024500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1789300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1787400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1928200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1696900</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>472900</v>
+      </c>
+      <c r="E47" s="3">
         <v>464900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>414700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>402300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>393800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>382500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>405800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>399500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>387600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>375000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>325500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>322200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>297200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>292600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>281800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>289800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>280300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>279800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>257300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>269600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>262200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>256200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>256800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>244800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>240500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>239100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>159100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>155000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>152400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>146300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>175100</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1097300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1121000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>797100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>809200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>804700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>805900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>756100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>766000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>780300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>787100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>766600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>777500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>716000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>693800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>675400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>680800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>703300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>728600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>711600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>721200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>724900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>554100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>487400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>490100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>492400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>493300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>495000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>492500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>482900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>473200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>478600</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10519300</v>
+      </c>
+      <c r="E49" s="3">
         <v>10612900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8762900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8728900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8751600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8714600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8444400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8407900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8531300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8607400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8525900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8613500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6993300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6848600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6833200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6823500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6843800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6810400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5978600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5951700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5979800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6015800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5365200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5399400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5365300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5129000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5104700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5098200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4876000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4553000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4626400</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,8 +4600,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4578,8 +4698,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14865000</v>
+      </c>
+      <c r="E54" s="3">
         <v>15023500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13093400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12839900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12616000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12431100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12038900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11985000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11972000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11898200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11679700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11755300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10579900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10357500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10433400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10311200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10601900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9844600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9219700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9069600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8891500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8662300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8108000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8152500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8058400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7796100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7783300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7535000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7298800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7100700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6977100</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,578 +4968,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>517400</v>
+      </c>
+      <c r="E57" s="3">
         <v>516600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>486600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>487700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>526100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>497100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>524300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>540700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>504200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>470300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>446400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>446500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>397100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>360400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>324800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>337500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>373900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>377200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>381900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>390400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>405600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>399600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>389100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>394300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>382300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>437300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>409400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>405900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>382800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>369500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>345500</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1055400</v>
+      </c>
+      <c r="E58" s="3">
         <v>1417900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>304500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>70000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>226100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>272000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>354800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>331400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>315100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>415700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>700000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>94700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>132300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>505000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>115900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>510800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>497400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>199500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>98400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>104200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>358900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>68700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>307700</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>308100</v>
       </c>
       <c r="AB58" s="3">
         <v>308100</v>
       </c>
       <c r="AC58" s="3">
+        <v>308100</v>
+      </c>
+      <c r="AD58" s="3">
         <v>509600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>272600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>338000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>278900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>613700</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>929800</v>
+      </c>
+      <c r="E59" s="3">
         <v>948100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>882700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>848100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>856600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>841000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>795100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>737600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>755100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>778000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>771800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>711100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>646700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>583300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>573600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>564100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>593000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>551200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>529000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>489800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>497400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>500300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>512000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>480600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>469500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>393200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>351400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>316700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>296000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>276000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>257600</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2502500</v>
+      </c>
+      <c r="E60" s="3">
         <v>2882600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1673700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1341200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1452700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1564200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1591400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1633000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1590700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1563300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1633800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1857600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1138500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1075900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1403500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1017500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1477700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1425900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1110500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>978600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1007200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1258700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>969900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1182500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1159900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1138700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1270300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>995100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1016800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>924400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1216700</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1877800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1895400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1856100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2186300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2175900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2158900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2085400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2147400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2204600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2229100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2238900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2262100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2256900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2281400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2295800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2753300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2741800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2271300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2229300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2368700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2368200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2273800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1832500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1838200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1897600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1866200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1920900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2128800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2076600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2062600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1516500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1515300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1221000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1231000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1230400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1231500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1229500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1254500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1245000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1233800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1248600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1292200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1063800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1050800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1029900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1054000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1056500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1031900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1014000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1055600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1059400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>887800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>793700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>793600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>796400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>763600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>825900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>818800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>801200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>857100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>846400</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5896800</v>
+      </c>
+      <c r="E66" s="3">
         <v>6293300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4750900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4758500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4858900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4954600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4906300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5034900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5040300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5026300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5121300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5412000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4459100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4408100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4729200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4824700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5275900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4729100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4353700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4402800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4434900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4420400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3596100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3814400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3854000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3768400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4017100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3942800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3894600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3844200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3603900</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10186600</v>
+      </c>
+      <c r="E72" s="3">
         <v>9940300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9655100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9372400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9105700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8857500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8600900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8353700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8121800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7900100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7664700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7453400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7267900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7094700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6915000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6751700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6626700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6387600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6198800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6010000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5826300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5653800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5474100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5315200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5153700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5002400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4784600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4651800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4522000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4403700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4315100</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8968200</v>
+      </c>
+      <c r="E76" s="3">
         <v>8730200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8342500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8081400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7757100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7476500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7132700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6950100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6931700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6871900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6558400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6343300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6120700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5949300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5704200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5486400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5326000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5115500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4866000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4666800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4456600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4241900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4511900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4338100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4204400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4027600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3766200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3592200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3404200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3256500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3373200</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>310900</v>
+      </c>
+      <c r="E81" s="3">
         <v>342900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>340400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>324200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>305700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>307100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>297600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>282400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>272400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>281700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>257500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>231700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>219200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>221000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>204600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>166200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>280600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>220800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>220700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>215500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>204300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>211500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>191200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>193900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>181300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>238500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>153500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>150500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>138900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>109100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E83" s="3">
         <v>91900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>81800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>81600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>82400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>88500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>75800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>77100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>78100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>77600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>74700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>75200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>64600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>64900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>63000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>61300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>66100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>64100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>55300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>57200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>57500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>53600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>48100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>48900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>48800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>52200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>44600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>43800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>42500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>56700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>410200</v>
+      </c>
+      <c r="E89" s="3">
         <v>540700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>472900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>335200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>386500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>385000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>327100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>235900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>201300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>281900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>307100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>287000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>284400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>385900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>309700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>314600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>270800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>342200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>329600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>246300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>196300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>296200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>248800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>203100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>177400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>252900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>239000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>199000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>142400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>247300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>169000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-59700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-28700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-27800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-20000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-58200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-28300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-26200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-43400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-23500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-37000</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-10100</v>
       </c>
       <c r="R91" s="3">
         <v>-10100</v>
       </c>
       <c r="S91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="T91" s="3">
         <v>-16900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-40800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-18200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-21900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-21400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-34600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-16300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-29400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-13400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2050100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-176300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-27800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-122200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-297200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-214500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-160700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1597600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-284500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-37100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-10800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>115600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-977600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-133700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-21900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-17800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-785800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-22500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-148200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-253600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-63400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-15700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-198400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-348300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-52400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-81800</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,13 +8351,14 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-57600</v>
+        <v>-64700</v>
       </c>
       <c r="E96" s="3">
         <v>-57600</v>
@@ -8133,70 +8367,70 @@
         <v>-57600</v>
       </c>
       <c r="G96" s="3">
+        <v>-57600</v>
+      </c>
+      <c r="H96" s="3">
         <v>-57500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-50500</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-50400</v>
       </c>
       <c r="J96" s="3">
         <v>-50400</v>
       </c>
       <c r="K96" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="L96" s="3">
         <v>-50800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-46300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-46200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-46100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-46000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-41300</v>
       </c>
       <c r="Q96" s="3">
         <v>-41300</v>
       </c>
       <c r="R96" s="3">
-        <v>-41200</v>
+        <v>-41300</v>
       </c>
       <c r="S96" s="3">
         <v>-41200</v>
       </c>
       <c r="T96" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="U96" s="3">
         <v>-32000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-31800</v>
       </c>
       <c r="W96" s="3">
         <v>-31800</v>
       </c>
       <c r="X96" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-32400</v>
       </c>
       <c r="Z96" s="3">
         <v>-32400</v>
       </c>
       <c r="AA96" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-32300</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-20700</v>
       </c>
       <c r="AC96" s="3">
         <v>-20700</v>
@@ -8205,16 +8439,19 @@
         <v>-20700</v>
       </c>
       <c r="AE96" s="3">
-        <v>-20600</v>
+        <v>-20700</v>
       </c>
       <c r="AF96" s="3">
         <v>-20600</v>
       </c>
       <c r="AG96" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-20700</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-417500</v>
+      </c>
+      <c r="E100" s="3">
         <v>1062100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-47700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-102100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-215000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-74500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-130800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-183000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-187400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-131900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-320400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>575600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-84000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-454700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-141100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-430300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>486600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>280800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-16400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-25700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-165900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>330300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-261700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-28500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-27100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-286200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-75100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>51900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>98400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-97900</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E101" s="3">
         <v>15300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-12500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>5100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>22200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-20500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-18400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>13900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>11300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-12600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>12200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-12000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-25600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>13700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>6600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>16500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>20800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>6900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-21600</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-432100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>236300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>205700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>54500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>35400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-38700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-32000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-733000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-89200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-92000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>173900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-122400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>860400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-342300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>167500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>199800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>14100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-164700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-39000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-89500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-90100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>219900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-53800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-147000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>271800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-10700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>AME</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1734800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1736200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1730900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1622800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1646100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1597100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1625700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1551800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1514600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1458500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1503700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1440700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1386300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1215700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1198900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1126900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1011900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1202200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1304800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1276600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1289400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1287700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1271300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1193000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1208900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1172600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1143100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1084800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1064600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1007700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>973000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1110400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1115500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1115900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1020900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1053200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1022500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1063700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1004600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>988200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>948800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>982400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>949400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>912700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>789400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>770000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>732700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>669200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>780900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>858200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>823300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>838200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>851300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>835300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>783000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>791200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>776800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>767000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>722100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>702200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>667400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>735600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>612700</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>624400</v>
+      </c>
+      <c r="E10" s="3">
         <v>620700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>615100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>601900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>592900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>574600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>562000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>547200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>526400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>509700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>521300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>491300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>473600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>426300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>428900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>394200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>342700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>421300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>446600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>453300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>451200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>436400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>436000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>410000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>417700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>395800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>376100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>362700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>362400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>340300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>237400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>332300</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,16 +1338,19 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>29200</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1347,8 +1367,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1356,8 +1376,8 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1365,20 +1385,20 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>-97100</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1395,8 +1415,8 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1493,8 +1516,8 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>8</v>
+      <c r="AA15" s="3">
+        <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>8</v>
@@ -1514,11 +1537,14 @@
       <c r="AG15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AH15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI15" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1287300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1319000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1285900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1184700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1227300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1191600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1227600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1167300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1149700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1105300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1142600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1103100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1069700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>922400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>900800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>856200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>784900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>829200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1007200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>975600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>994000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1004400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>989300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>927700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>938800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>914500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>913500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>854800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>835100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>790200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>799700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>743900</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>447500</v>
+      </c>
+      <c r="E18" s="3">
         <v>417200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>445000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>438100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>418800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>405500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>398100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>384500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>364900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>353200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>361100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>337600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>316600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>293300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>298100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>270700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>227000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>373000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>297600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>301000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>295400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>283300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>282000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>265300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>270100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>258100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>229600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>230000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>229500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>217500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>173300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>201100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4400</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-1900</v>
       </c>
       <c r="Q20" s="3">
         <v>-1900</v>
       </c>
       <c r="R20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-6600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2900</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA20" s="3">
         <v>-1000</v>
       </c>
       <c r="AB20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-7800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-4400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>546300</v>
+      </c>
+      <c r="E21" s="3">
         <v>514600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>533000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>513700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>496700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>482500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>490000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>463500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>443900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>433900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>437400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>414800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>387400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>356000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>361000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>332300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>290500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>439900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>355100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>350800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>349200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>337100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>332700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>312500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>317900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>306300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>274000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>273800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>271800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>258500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>225600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E22" s="3">
         <v>35300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>24100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>18400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>20600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>23000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>19600</v>
-      </c>
-      <c r="M22" s="3">
-        <v>20500</v>
       </c>
       <c r="N22" s="3">
         <v>20500</v>
       </c>
       <c r="O22" s="3">
+        <v>20500</v>
+      </c>
+      <c r="P22" s="3">
         <v>20400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>18900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>19500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>21200</v>
-      </c>
-      <c r="S22" s="3">
-        <v>22700</v>
       </c>
       <c r="T22" s="3">
         <v>22700</v>
       </c>
       <c r="U22" s="3">
+        <v>22700</v>
+      </c>
+      <c r="V22" s="3">
         <v>23000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>21300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>21500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>22700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>20300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>19400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>20800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>21700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>24300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>24700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>24600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>24500</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>23600</v>
       </c>
       <c r="AH22" s="3">
         <v>23600</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>23600</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>417000</v>
+      </c>
+      <c r="E23" s="3">
         <v>381300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>416900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>413500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>396400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>379600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>378500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>367500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>346500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>336200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>339300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>319700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>291800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>272500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>276700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>248100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>206500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>351100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>268000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>274200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>270600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>256900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>258800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>244900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>248200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>235800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>197500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>204400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>203400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>191400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>145300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>79300</v>
+      </c>
+      <c r="E24" s="3">
         <v>70400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>74100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>73100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>72100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>73900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>71400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>69900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>64100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>63800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>57600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>62200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>60100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>53200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>55700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>43500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>40200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>70500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>47200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>53500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>55100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>52700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>59100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>53700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>54400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>54500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>50600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>50900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>52900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>52500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>36100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>337700</v>
+      </c>
+      <c r="E26" s="3">
         <v>310900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>342900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>340400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>324200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>305700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>307100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>297600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>282400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>272400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>281700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>257500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>231700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>219200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>221000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>204600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>166200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>280600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>220800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>220700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>215500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>204300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>199700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>191200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>193900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>181300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>146900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>153500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>150500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>138900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>109100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>337700</v>
+      </c>
+      <c r="E27" s="3">
         <v>310900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>342900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>340400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>324200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>305700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>307100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>297600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>282400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>272400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>281700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>257500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>231700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>219200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>221000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>204600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>166200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>280600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>220800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>220700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>215500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>204300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>199700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>191200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>193900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>181300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>146900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>153500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>150500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>138900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>109100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2714,8 +2775,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2732,11 +2793,11 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>11800</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2744,11 +2805,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>91600</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4400</v>
-      </c>
-      <c r="P32" s="3">
-        <v>1900</v>
       </c>
       <c r="Q32" s="3">
         <v>1900</v>
       </c>
       <c r="R32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="S32" s="3">
         <v>1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>6600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2900</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>1000</v>
       </c>
       <c r="AA32" s="3">
         <v>1000</v>
       </c>
       <c r="AB32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC32" s="3">
         <v>600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>7800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>4400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>337700</v>
+      </c>
+      <c r="E33" s="3">
         <v>310900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>342900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>340400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>324200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>305700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>307100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>297600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>282400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>272400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>281700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>257500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>231700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>219200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>221000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>204600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>166200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>280600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>220800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>220700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>215500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>204300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>211500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>191200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>193900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>181300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>238500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>153500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>150500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>138900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>109100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>337700</v>
+      </c>
+      <c r="E35" s="3">
         <v>310900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>342900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>340400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>324200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>305700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>307100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>297600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>282400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>272400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>281700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>257500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>231700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>219200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>221000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>204600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>166200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>280600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>220800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>220700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>215500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>204300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>211500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>191200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>193900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>181300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>238500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>153500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>150500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>138900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>109100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>396600</v>
+      </c>
+      <c r="E41" s="3">
         <v>373800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>409800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>841900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>605600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>399900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>345400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>309900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>348700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>340300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>346800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>358700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>390600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1123700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1212800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1304800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1131000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1253400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>393000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>735400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>567900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>368100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>354000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>518700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>557700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>556800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>646300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>736400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>516500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>570200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>717300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>445500</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,694 +3811,718 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1126100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1130800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1153800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1076600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1074400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1028900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1039100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>988100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>993000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>957200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>924500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>851400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>827900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>749900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>666400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>682900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>688000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>793000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>817800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>840000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>839600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>839500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>732800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>714900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>711000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>684600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>668200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>640800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>642300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>603900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>592300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>595100</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1101700</v>
+      </c>
+      <c r="E44" s="3">
         <v>1127300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1132500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1087600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1107800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1117100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1044300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1025100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>966600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>866500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>769200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>738700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>711600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>604300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>559200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>584800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>621500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>654300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>624600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>623700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>634100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>640600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>624700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>620100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>614400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>596300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>540500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>546900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>541200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>529900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>492100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>537200</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>142800</v>
+      </c>
+      <c r="E45" s="3">
         <v>143600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>128600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>112600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>111800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>120100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>99300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>109300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>103400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>108900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>88300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>113100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>111900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>95600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>84000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>70500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>76700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>73800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>190400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>73200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>85500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>76500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>124600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>144800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>135100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>122500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>79700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>100400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>89300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>83400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>126500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>119100</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2767200</v>
+      </c>
+      <c r="E46" s="3">
         <v>2775500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2824700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3118700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2899600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2665900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2528100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2432600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2411600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2272800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2128800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2061800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2042100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2573500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2522500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2643000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2517100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2774500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2025800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2272200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2127200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1924600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1836100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1998600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2018100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1960200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1934700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2024500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1789300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1787400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1928200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1696900</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>483000</v>
+      </c>
+      <c r="E47" s="3">
         <v>472900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>464900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>414700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>402300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>393800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>382500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>405800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>399500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>387600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>375000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>325500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>322200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>297200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>292600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>281800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>289800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>280300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>279800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>257300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>269600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>262200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>256200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>256800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>244800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>240500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>239100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>159100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>155000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>152400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>146300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>175100</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1079000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1097300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1121000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>797100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>809200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>804700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>805900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>756100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>766000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>780300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>787100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>766600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>777500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>716000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>693800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>675400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>680800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>703300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>728600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>711600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>721200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>724900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>554100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>487400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>490100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>492400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>493300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>495000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>492500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>482900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>473200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>478600</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10466600</v>
+      </c>
+      <c r="E49" s="3">
         <v>10519300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10612900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8762900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8728900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8751600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8714600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8444400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8407900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8531300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8607400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8525900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8613500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6993300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6848600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6833200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6823500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6843800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6810400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5978600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5951700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5979800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6015800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5365200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5399400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5365300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5129000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5104700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5098200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4876000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4553000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4626400</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14795900</v>
+      </c>
+      <c r="E54" s="3">
         <v>14865000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15023500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13093400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12839900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12616000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12431100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12038900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11985000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11972000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11898200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11679700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11755300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10579900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10357500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10433400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10311200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10601900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9844600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9219700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9069600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>8891500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8662300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8108000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8152500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8058400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7796100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7783300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7535000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7298800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7100700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6977100</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>510500</v>
+      </c>
+      <c r="E57" s="3">
         <v>517400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>516600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>486600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>487700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>526100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>497100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>524300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>540700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>504200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>470300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>446400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>446500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>397100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>360400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>324800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>337500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>373900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>377200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>381900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>390400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>405600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>399600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>389100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>394300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>382300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>437300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>409400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>405900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>382800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>369500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>345500</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>828000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1055400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1417900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>304500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>70000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>226100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>272000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>354800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>331400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>315100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>415700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>700000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>94700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>132300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>505000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>115900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>510800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>497400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>199500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>98400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>104200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>358900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>68700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>307700</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>308100</v>
       </c>
       <c r="AC58" s="3">
         <v>308100</v>
       </c>
       <c r="AD58" s="3">
+        <v>308100</v>
+      </c>
+      <c r="AE58" s="3">
         <v>509600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>272600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>338000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>278900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>613700</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>864600</v>
+      </c>
+      <c r="E59" s="3">
         <v>929800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>948100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>882700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>848100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>856600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>841000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>795100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>737600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>755100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>778000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>771800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>711100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>646700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>583300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>573600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>564100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>593000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>551200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>529000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>489800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>497400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>500300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>512000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>480600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>469500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>393200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>351400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>316700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>296000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>276000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>257600</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2203000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2502500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2882600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1673700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1341200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1452700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1564200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1591400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1633000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1590700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1563300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1633800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1857600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1138500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1075900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1403500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1017500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1477700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1425900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1110500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>978600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1007200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1258700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>969900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1182500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1159900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1138700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1270300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>995100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1016800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>924400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1216700</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1823400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1877800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1895400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1856100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2186300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2175900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2158900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2085400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2147400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2204600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2229100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2238900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2262100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2256900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2281400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2295800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2753300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2741800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2271300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2229300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2368700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2368200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2273800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1832500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1838200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1897600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1866200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1920900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2128800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2076600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2062600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1517000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1516500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1515300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1221000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1231000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1230400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1231500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1229500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1254500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1245000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1233800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1248600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1292200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1063800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1050800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1029900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1054000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1056500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1031900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1014000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1055600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1059400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>887800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>793700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>793600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>796400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>763600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>825900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>818800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>801200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>857100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>846400</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5543500</v>
+      </c>
+      <c r="E66" s="3">
         <v>5896800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6293300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4750900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4758500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4858900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4954600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4906300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5034900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5040300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5026300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5121300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5412000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4459100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4408100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4729200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4824700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5275900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4729100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4353700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4402800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4434900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4420400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3596100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3814400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3854000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3768400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4017100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3942800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3894600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3844200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3603900</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10459600</v>
+      </c>
+      <c r="E72" s="3">
         <v>10186600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9940300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9655100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9372400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9105700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8857500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8600900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8353700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8121800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7900100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7664700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7453400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7267900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7094700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6915000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6751700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6626700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6387600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6198800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6010000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5826300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5653800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5474100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5315200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5153700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5002400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4784600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4651800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4522000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4403700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4315100</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9252400</v>
+      </c>
+      <c r="E76" s="3">
         <v>8968200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8730200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8342500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8081400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7757100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7476500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7132700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6950100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6931700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6871900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6558400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6343300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6120700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5949300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5704200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5486400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5326000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5115500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4866000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4666800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4456600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4241900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4511900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4338100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4204400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4027600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3766200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3592200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3404200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3256500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3373200</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>337700</v>
+      </c>
+      <c r="E81" s="3">
         <v>310900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>342900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>340400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>324200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>305700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>307100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>297600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>282400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>272400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>281700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>257500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>231700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>219200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>221000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>204600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>166200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>280600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>220800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>220700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>215500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>204300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>211500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>191200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>193900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>181300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>238500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>153500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>150500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>138900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>109100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>98700</v>
+      </c>
+      <c r="E83" s="3">
         <v>98000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>91900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>81800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>81600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>82400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>88500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>75800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>77100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>78100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>77600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>74700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>75200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>64600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>64900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>63000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>61300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>66100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>64100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>55300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>57200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>57500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>53600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>48100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>48900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>48800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>52200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>44600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>43800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>42500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>56700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>381400</v>
+      </c>
+      <c r="E89" s="3">
         <v>410200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>540700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>472900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>335200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>386500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>385000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>327100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>235900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>201300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>281900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>307100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>287000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>284400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>385900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>309700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>314600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>270800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>342200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>329600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>246300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>196300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>296200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>248800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>203100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>177400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>252900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>239000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>199000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>142400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>247300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>169000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-27700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-59700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-28700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-27800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-20000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-58200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-28300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-26200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-43400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-26200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-23500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-37000</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-10100</v>
       </c>
       <c r="S91" s="3">
         <v>-10100</v>
       </c>
       <c r="T91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="U91" s="3">
         <v>-16900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-40800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-18200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-21900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-21400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-34600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-16300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-29400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-13400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2050100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-176300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-122200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-297200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-214500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-26200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-160700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1597600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-284500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-37100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>115600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-977600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-133700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-21900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-17800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-785800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-22500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-148200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-253600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-63400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-15700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-198400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-348300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-52400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-81800</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8361,7 +8595,7 @@
         <v>-64700</v>
       </c>
       <c r="E96" s="3">
-        <v>-57600</v>
+        <v>-64700</v>
       </c>
       <c r="F96" s="3">
         <v>-57600</v>
@@ -8370,70 +8604,70 @@
         <v>-57600</v>
       </c>
       <c r="H96" s="3">
+        <v>-57600</v>
+      </c>
+      <c r="I96" s="3">
         <v>-57500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-50500</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-50400</v>
       </c>
       <c r="K96" s="3">
         <v>-50400</v>
       </c>
       <c r="L96" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="M96" s="3">
         <v>-50800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-46300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-46200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-46100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-46000</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-41300</v>
       </c>
       <c r="R96" s="3">
         <v>-41300</v>
       </c>
       <c r="S96" s="3">
-        <v>-41200</v>
+        <v>-41300</v>
       </c>
       <c r="T96" s="3">
         <v>-41200</v>
       </c>
       <c r="U96" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="V96" s="3">
         <v>-32000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-31800</v>
       </c>
       <c r="X96" s="3">
         <v>-31800</v>
       </c>
       <c r="Y96" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-32400</v>
       </c>
       <c r="AA96" s="3">
         <v>-32400</v>
       </c>
       <c r="AB96" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-32300</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-20700</v>
       </c>
       <c r="AD96" s="3">
         <v>-20700</v>
@@ -8442,16 +8676,19 @@
         <v>-20700</v>
       </c>
       <c r="AF96" s="3">
-        <v>-20600</v>
+        <v>-20700</v>
       </c>
       <c r="AG96" s="3">
         <v>-20600</v>
       </c>
       <c r="AH96" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-20700</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-334100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-417500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1062100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-47700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-102100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-215000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-74500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-130800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-183000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-187400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-131900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-320400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>575600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-84000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-454700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-141100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-430300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>486600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>280800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-16400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-25700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-165900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>330300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-261700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-28500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-27100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-286200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-75100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>51900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>98400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-97900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>15300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-12500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>5100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>22200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-20500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-18400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>13900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>11300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-12600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>12200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-12000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-25600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>13700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>6600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>16500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>20800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>6900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-21600</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-36000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-432100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>236300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>205700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>54500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>35400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-38700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-11900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-32000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-733000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-89200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-92000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>173900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-122400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>860400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-342300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>167500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>199800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>14100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-164700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-39000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-89500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-90100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>219900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-53800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-147000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>271800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-10700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>AME</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1708600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1734800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1736200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1730900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1622800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1646100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1597100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1625700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1551800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1514600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1458500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1503700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1440700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1386300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1215700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1198900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1126900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1011900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1202200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1304800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1276600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1289400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1287700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1271300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1193000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1208900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1172600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1143100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1084800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1064600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1007700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>973000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1092800</v>
+      </c>
+      <c r="E9" s="3">
         <v>1110400</v>
       </c>
-      <c r="E9" s="3">
-        <v>1115500</v>
-      </c>
       <c r="F9" s="3">
+        <v>1144700</v>
+      </c>
+      <c r="G9" s="3">
         <v>1115900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1020900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1053200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1022500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1063700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1004600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>988200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>948800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>982400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>949400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>912700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>789400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>770000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>732700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>669200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>780900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>858200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>823300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>838200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>851300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>835300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>783000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>791200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>776800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>767000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>722100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>702200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>667400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>735600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>612700</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>615800</v>
+      </c>
+      <c r="E10" s="3">
         <v>624400</v>
       </c>
-      <c r="E10" s="3">
-        <v>620700</v>
-      </c>
       <c r="F10" s="3">
-        <v>615100</v>
+        <v>591500</v>
       </c>
       <c r="G10" s="3">
+        <v>615000</v>
+      </c>
+      <c r="H10" s="3">
         <v>601900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>592900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>574600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>562000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>547200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>526400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>509700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>521300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>491300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>473600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>426300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>428900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>394200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>342700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>421300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>446600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>453300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>451200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>436400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>436000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>410000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>417700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>395800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>376100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>362700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>362400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>340300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>237400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>332300</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1167,8 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>351700</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,16 +1358,19 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>29200</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1370,8 +1390,8 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1379,8 +1399,8 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1388,20 +1408,20 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>-97100</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1418,8 +1438,8 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1442,31 +1462,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>90400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>98700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>98000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>91900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>81800</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>81600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>82400</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1519,8 +1542,8 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>8</v>
+      <c r="AB15" s="3">
+        <v>0</v>
       </c>
       <c r="AC15" s="3" t="s">
         <v>8</v>
@@ -1540,11 +1563,14 @@
       <c r="AH15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AI15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1287300</v>
+        <v>1270400</v>
       </c>
       <c r="E17" s="3">
-        <v>1319000</v>
+        <v>1296300</v>
       </c>
       <c r="F17" s="3">
-        <v>1285900</v>
+        <v>1330900</v>
       </c>
       <c r="G17" s="3">
-        <v>1184700</v>
+        <v>1253400</v>
       </c>
       <c r="H17" s="3">
-        <v>1227300</v>
+        <v>1194000</v>
       </c>
       <c r="I17" s="3">
-        <v>1191600</v>
+        <v>1237200</v>
       </c>
       <c r="J17" s="3">
+        <v>1205000</v>
+      </c>
+      <c r="K17" s="3">
         <v>1227600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1167300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1149700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1105300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1142600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1103100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1069700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>922400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>900800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>856200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>784900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>829200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1007200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>975600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>994000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1004400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>989300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>927700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>938800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>914500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>913500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>854800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>835100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>790200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>799700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>743900</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>447500</v>
+        <v>438100</v>
       </c>
       <c r="E18" s="3">
-        <v>417200</v>
+        <v>438600</v>
       </c>
       <c r="F18" s="3">
-        <v>445000</v>
+        <v>405200</v>
       </c>
       <c r="G18" s="3">
-        <v>438100</v>
+        <v>477500</v>
       </c>
       <c r="H18" s="3">
-        <v>418800</v>
+        <v>428900</v>
       </c>
       <c r="I18" s="3">
-        <v>405500</v>
+        <v>408900</v>
       </c>
       <c r="J18" s="3">
+        <v>392100</v>
+      </c>
+      <c r="K18" s="3">
         <v>398100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>384500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>364900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>353200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>361100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>337600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>316600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>293300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>298100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>270700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>227000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>373000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>297600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>301000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>295400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>283300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>282000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>265300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>270100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>258100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>229600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>230000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>229500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>217500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>173300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>201100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>-5800</v>
       </c>
       <c r="E20" s="3">
-        <v>-700</v>
+        <v>-9100</v>
       </c>
       <c r="F20" s="3">
-        <v>-4000</v>
+        <v>-11300</v>
       </c>
       <c r="G20" s="3">
+        <v>48500</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-6200</v>
       </c>
-      <c r="H20" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-5400</v>
-      </c>
       <c r="J20" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="K20" s="3">
         <v>3400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4400</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-1900</v>
       </c>
       <c r="R20" s="3">
         <v>-1900</v>
       </c>
       <c r="S20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="T20" s="3">
         <v>-1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-6600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-1000</v>
       </c>
       <c r="AB20" s="3">
         <v>-1000</v>
       </c>
       <c r="AC20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-7800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-4400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>534300</v>
+      </c>
+      <c r="E21" s="3">
         <v>546300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>514600</v>
       </c>
-      <c r="F21" s="3">
-        <v>533000</v>
-      </c>
       <c r="G21" s="3">
+        <v>521000</v>
+      </c>
+      <c r="H21" s="3">
         <v>513700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>496700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>482500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>490000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>463500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>443900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>433900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>437400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>414800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>387400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>356000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>361000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>332300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>290500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>439900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>355100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>350800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>349200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>337100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>332700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>312500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>317900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>306300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>274000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>273800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>271800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>258500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>225600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E22" s="3">
         <v>30600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>35300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>24100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>18700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>20600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>23000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>19600</v>
-      </c>
-      <c r="N22" s="3">
-        <v>20500</v>
       </c>
       <c r="O22" s="3">
         <v>20500</v>
       </c>
       <c r="P22" s="3">
+        <v>20500</v>
+      </c>
+      <c r="Q22" s="3">
         <v>20400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>18900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>19500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>21200</v>
-      </c>
-      <c r="T22" s="3">
-        <v>22700</v>
       </c>
       <c r="U22" s="3">
         <v>22700</v>
       </c>
       <c r="V22" s="3">
+        <v>22700</v>
+      </c>
+      <c r="W22" s="3">
         <v>23000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>21300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>21500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>22700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>20300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>19400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>20800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>21700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>24300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>24700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>24600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>24500</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>23600</v>
       </c>
       <c r="AI22" s="3">
         <v>23600</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>23600</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>418800</v>
+      </c>
+      <c r="E23" s="3">
         <v>417000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>381300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>416900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>413500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>396400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>379600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>378500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>367500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>346500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>336200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>339300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>319700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>291800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>272500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>276700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>248100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>206500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>351100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>268000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>274200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>270600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>256900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>258800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>244900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>248200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>235800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>197500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>204400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>203400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>191400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>145300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E24" s="3">
         <v>79300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>70400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>74100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>73100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>72100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>73900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>71400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>69900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>64100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>63800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>57600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>62200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>60100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>53200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>55700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>43500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>40200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>70500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>47200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>53500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>55100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>52700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>59100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>53700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>54400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>54500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>50600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>50900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>52900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>52500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>36100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>340200</v>
+      </c>
+      <c r="E26" s="3">
         <v>337700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>310900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>342900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>340400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>324200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>305700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>307100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>297600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>282400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>272400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>281700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>257500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>231700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>219200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>221000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>204600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>166200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>280600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>220800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>220700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>215500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>204300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>199700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>191200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>193900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>181300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>146900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>153500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>150500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>138900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>109100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>340200</v>
+      </c>
+      <c r="E27" s="3">
         <v>337700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>310900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>342900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>340400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>324200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>305700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>307100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>297600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>282400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>272400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>281700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>257500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>231700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>219200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>221000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>204600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>166200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>280600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>220800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>220700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>215500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>204300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>199700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>191200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>193900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>181300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>146900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>153500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>150500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>138900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>109100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2778,8 +2839,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2796,11 +2857,11 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>11800</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2808,11 +2869,11 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>91600</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>5800</v>
       </c>
       <c r="E32" s="3">
-        <v>700</v>
+        <v>9100</v>
       </c>
       <c r="F32" s="3">
-        <v>4000</v>
+        <v>11300</v>
       </c>
       <c r="G32" s="3">
+        <v>-48500</v>
+      </c>
+      <c r="H32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I32" s="3">
         <v>6200</v>
       </c>
-      <c r="H32" s="3">
-        <v>3700</v>
-      </c>
-      <c r="I32" s="3">
-        <v>5400</v>
-      </c>
       <c r="J32" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4400</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>1900</v>
       </c>
       <c r="R32" s="3">
         <v>1900</v>
       </c>
       <c r="S32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T32" s="3">
         <v>1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>6600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2900</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>1000</v>
       </c>
       <c r="AB32" s="3">
         <v>1000</v>
       </c>
       <c r="AC32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD32" s="3">
         <v>600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>7800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>4400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>340200</v>
+      </c>
+      <c r="E33" s="3">
         <v>337700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>310900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>342900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>340400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>324200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>305700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>307100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>297600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>282400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>272400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>281700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>257500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>231700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>219200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>221000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>204600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>166200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>280600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>220800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>220700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>215500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>204300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>211500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>191200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>193900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>181300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>238500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>153500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>150500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>138900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>109100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>340200</v>
+      </c>
+      <c r="E35" s="3">
         <v>337700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>310900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>342900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>340400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>324200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>305700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>307100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>297600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>282400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>272400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>281700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>257500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>231700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>219200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>221000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>204600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>166200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>280600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>220800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>220700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>215500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>204300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>211500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>191200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>193900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>181300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>238500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>153500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>150500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>138900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>109100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>396300</v>
+      </c>
+      <c r="E41" s="3">
         <v>396600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>373800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>409800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>841900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>605600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>399900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>345400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>309900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>348700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>340300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>346800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>358700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>390600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1123700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1212800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1304800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1131000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1253400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>393000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>735400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>567900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>368100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>354000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>518700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>557700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>556800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>646300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>736400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>516500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>570200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>717300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>445500</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,715 +3904,739 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1119700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1126100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1130800</v>
       </c>
-      <c r="F43" s="3">
-        <v>1153800</v>
-      </c>
       <c r="G43" s="3">
+        <v>1070200</v>
+      </c>
+      <c r="H43" s="3">
         <v>1076600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1074400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1028900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1039100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>988100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>993000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>957200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>924500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>851400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>827900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>749900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>666400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>682900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>688000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>793000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>817800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>840000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>839600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>839500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>732800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>714900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>711000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>684600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>668200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>640800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>642300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>603900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>592300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>595100</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1084600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1101700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1127300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1132500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1087600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1107800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1117100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1044300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1025100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>966600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>866500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>769200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>738700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>711600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>604300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>559200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>584800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>621500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>654300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>624600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>623700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>634100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>640600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>624700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>620100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>614400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>596300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>540500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>546900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>541200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>529900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>492100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>537200</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>133100</v>
+      </c>
+      <c r="E45" s="3">
         <v>142800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>143600</v>
       </c>
-      <c r="F45" s="3">
-        <v>128600</v>
-      </c>
       <c r="G45" s="3">
+        <v>212200</v>
+      </c>
+      <c r="H45" s="3">
         <v>112600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>111800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>120100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>99300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>109300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>103400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>108900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>88300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>113100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>111900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>95600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>84000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>70500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>76700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>73800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>190400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>73200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>85500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>76500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>124600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>144800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>135100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>122500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>79700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>100400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>89300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>83400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>126500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>119100</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2733700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2767200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2775500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2824700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3118700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2899600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2665900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2528100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2432600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2411600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2272800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2128800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2061800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2042100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2573500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2522500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2643000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2517100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2774500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2025800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2272200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2127200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1924600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1836100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1998600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2018100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1960200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1934700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2024500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1789300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1787400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1928200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1696900</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>483000</v>
+        <v>10900</v>
       </c>
       <c r="E47" s="3">
-        <v>472900</v>
+        <v>12000</v>
       </c>
       <c r="F47" s="3">
-        <v>464900</v>
+        <v>12400</v>
       </c>
       <c r="G47" s="3">
-        <v>414700</v>
+        <v>11900</v>
       </c>
       <c r="H47" s="3">
-        <v>402300</v>
+        <v>11000</v>
       </c>
       <c r="I47" s="3">
-        <v>393800</v>
+        <v>10500</v>
       </c>
       <c r="J47" s="3">
+        <v>10400</v>
+      </c>
+      <c r="K47" s="3">
         <v>382500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>405800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>399500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>387600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>375000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>325500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>322200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>297200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>292600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>281800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>289800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>280300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>279800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>257300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>269600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>262200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>256200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>256800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>244800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>240500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>239100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>159100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>155000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>152400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>146300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>175100</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1034000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1079000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1097300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1121000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>797100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>809200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>804700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>805900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>756100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>766000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>780300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>787100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>766600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>777500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>716000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>693800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>675400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>680800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>703300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>728600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>711600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>721200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>724900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>554100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>487400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>490100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>492400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>493300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>495000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>492500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>482900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>473200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>478600</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10501300</v>
+      </c>
+      <c r="E49" s="3">
         <v>10466600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10519300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10612900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8762900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8728900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8751600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8714600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8444400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8407900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8531300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8607400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8525900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8613500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6993300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6848600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6833200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6823500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6843800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6810400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5978600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5951700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5979800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6015800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5365200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5399400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5365300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5129000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5104700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5098200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4876000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4553000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4626400</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,31 +4840,34 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>487800</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>470900</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>460500</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>378700</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>403700</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>391700</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>383400</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14767600</v>
+      </c>
+      <c r="E54" s="3">
         <v>14795900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14865000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15023500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13093400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12839900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12616000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12431100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12038900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11985000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11972000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11898200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11679700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11755300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10579900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10357500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10433400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10311200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10601900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9844600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9219700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9069600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>8891500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8662300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8108000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8152500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8058400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7796100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7783300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7535000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7298800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7100700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6977100</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>511700</v>
+      </c>
+      <c r="E57" s="3">
         <v>510500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>517400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>516600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>486600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>487700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>526100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>497100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>524300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>540700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>504200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>470300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>446400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>446500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>397100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>360400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>324800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>337500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>373900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>377200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>381900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>390400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>405600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>399600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>389100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>394300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>382300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>437300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>409400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>405900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>382800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>369500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>345500</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>828000</v>
+        <v>625400</v>
       </c>
       <c r="E58" s="3">
-        <v>1055400</v>
+        <v>886700</v>
       </c>
       <c r="F58" s="3">
-        <v>1417900</v>
+        <v>1115500</v>
       </c>
       <c r="G58" s="3">
-        <v>304500</v>
+        <v>1479000</v>
       </c>
       <c r="H58" s="3">
-        <v>5400</v>
+        <v>349400</v>
       </c>
       <c r="I58" s="3">
-        <v>70000</v>
+        <v>51600</v>
       </c>
       <c r="J58" s="3">
+        <v>116500</v>
+      </c>
+      <c r="K58" s="3">
         <v>226100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>272000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>354800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>331400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>315100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>415700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>700000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>94700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>132300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>505000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>115900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>510800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>497400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>199500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>98400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>104200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>358900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>68700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>307700</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>308100</v>
       </c>
       <c r="AD58" s="3">
         <v>308100</v>
       </c>
       <c r="AE58" s="3">
+        <v>308100</v>
+      </c>
+      <c r="AF58" s="3">
         <v>509600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>272600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>338000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>278900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>613700</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>864600</v>
+        <v>519800</v>
       </c>
       <c r="E59" s="3">
-        <v>929800</v>
+        <v>461800</v>
       </c>
       <c r="F59" s="3">
-        <v>948100</v>
+        <v>513900</v>
       </c>
       <c r="G59" s="3">
-        <v>882700</v>
+        <v>658600</v>
       </c>
       <c r="H59" s="3">
-        <v>848100</v>
+        <v>456100</v>
       </c>
       <c r="I59" s="3">
-        <v>856600</v>
+        <v>459600</v>
       </c>
       <c r="J59" s="3">
+        <v>511800</v>
+      </c>
+      <c r="K59" s="3">
         <v>841000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>795100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>737600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>755100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>778000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>771800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>711100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>646700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>583300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>573600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>564100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>593000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>551200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>529000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>489800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>497400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>500300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>512000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>480600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>469500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>393200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>351400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>316700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>296000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>276000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>257600</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1966900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2203000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2502500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2882600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1673700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1341200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1452700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1564200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1591400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1633000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1590700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1563300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1633800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1857600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1138500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1075900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1403500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1017500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1477700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1425900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1110500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>978600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1007200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1258700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>969900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1182500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1159900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1138700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1270300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>995100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1016800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>924400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1216700</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1823400</v>
+        <v>1931900</v>
       </c>
       <c r="E61" s="3">
-        <v>1877800</v>
+        <v>1996000</v>
       </c>
       <c r="F61" s="3">
-        <v>1895400</v>
+        <v>2051600</v>
       </c>
       <c r="G61" s="3">
-        <v>1856100</v>
+        <v>2077900</v>
       </c>
       <c r="H61" s="3">
-        <v>2186300</v>
+        <v>1980600</v>
       </c>
       <c r="I61" s="3">
-        <v>2175900</v>
+        <v>2315900</v>
       </c>
       <c r="J61" s="3">
+        <v>2300900</v>
+      </c>
+      <c r="K61" s="3">
         <v>2158900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2085400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2147400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2204600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2229100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2238900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2262100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2256900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2281400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2295800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2753300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2741800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2271300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2229300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2368700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2368200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2273800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1832500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1838200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1897600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1866200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1920900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2128800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2076600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2062600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1517000</v>
+        <v>480700</v>
       </c>
       <c r="E62" s="3">
-        <v>1516500</v>
+        <v>477800</v>
       </c>
       <c r="F62" s="3">
-        <v>1515300</v>
+        <v>458600</v>
       </c>
       <c r="G62" s="3">
-        <v>1221000</v>
+        <v>438900</v>
       </c>
       <c r="H62" s="3">
-        <v>1231000</v>
+        <v>407600</v>
       </c>
       <c r="I62" s="3">
-        <v>1230400</v>
+        <v>387600</v>
       </c>
       <c r="J62" s="3">
+        <v>380300</v>
+      </c>
+      <c r="K62" s="3">
         <v>1231500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1229500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1254500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1245000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1233800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1248600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1292200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1063800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1050800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1029900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1054000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1056500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1031900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1014000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1055600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1059400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>887800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>793700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>793600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>796400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>763600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>825900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>818800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>801200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>857100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>846400</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5217400</v>
+      </c>
+      <c r="E66" s="3">
         <v>5543500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5896800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6293300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4750900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4758500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4858900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4954600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4906300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5034900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5040300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5026300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5121300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5412000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4459100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4408100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4729200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4824700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5275900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4729100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4353700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4402800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4434900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4420400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3596100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3814400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3854000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3768400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4017100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3942800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3894600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3844200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3603900</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10735100</v>
+      </c>
+      <c r="E72" s="3">
         <v>10459600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10186600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9940300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9655100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9372400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9105700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8857500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8600900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8353700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8121800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7900100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7664700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7453400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7267900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7094700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6915000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6751700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6626700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6387600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6198800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6010000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5826300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5653800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5474100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5315200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5153700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5002400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4784600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4651800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4522000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4403700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4315100</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9550200</v>
+      </c>
+      <c r="E76" s="3">
         <v>9252400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8968200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8730200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8342500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8081400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7757100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7476500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7132700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6950100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6931700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6871900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6558400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6343300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6120700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5949300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5704200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5486400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5326000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5115500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4866000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4666800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4456600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4241900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4511900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4338100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4204400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4027600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3766200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3592200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3404200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3256500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3373200</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>340200</v>
+      </c>
+      <c r="E81" s="3">
         <v>337700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>310900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>342900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>340400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>324200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>305700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>307100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>297600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>282400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>272400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>281700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>257500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>231700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>219200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>221000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>204600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>166200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>280600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>220800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>220700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>215500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>204300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>211500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>191200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>193900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>181300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>238500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>153500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>150500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>138900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>109100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>98700</v>
+        <v>81800</v>
       </c>
       <c r="E83" s="3">
-        <v>98000</v>
+        <v>81600</v>
       </c>
       <c r="F83" s="3">
-        <v>91900</v>
+        <v>82400</v>
       </c>
       <c r="G83" s="3">
-        <v>81800</v>
+        <v>88500</v>
       </c>
       <c r="H83" s="3">
-        <v>81600</v>
+        <v>75800</v>
       </c>
       <c r="I83" s="3">
-        <v>82400</v>
+        <v>77100</v>
       </c>
       <c r="J83" s="3">
+        <v>78100</v>
+      </c>
+      <c r="K83" s="3">
         <v>88500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>75800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>77100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>78100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>77600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>74700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>75200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>64600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>64900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>63000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>61300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>66100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>64100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>55300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>57200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>57500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>53600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>48100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>48900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>48800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>52200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>44600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>43800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>42500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>56700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>487200</v>
+      </c>
+      <c r="E89" s="3">
         <v>381400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>410200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>540700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>472900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>335200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>386500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>385000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>327100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>235900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>201300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>281900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>307100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>287000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>284400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>385900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>309700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>314600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>270800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>342200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>329600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>246300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>196300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>296200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>248800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>203100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>177400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>252900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>239000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>199000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>142400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>247300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>169000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-27700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-59700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-28700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-27800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-58200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-28300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-26200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-43400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-26200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-23500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-17500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-37000</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-10100</v>
       </c>
       <c r="T91" s="3">
         <v>-10100</v>
       </c>
       <c r="U91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="V91" s="3">
         <v>-16900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-40800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-18200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-21900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-21400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-34600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-16300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-12300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-29400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-13400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-22100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-21400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2050100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-176300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-27800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-122200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-297200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-214500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-160700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1597600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-284500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-37100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>115600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-977600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-133700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-21900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-17800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-785800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-22500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-148200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-253600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-63400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-15700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-198400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-348300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-52400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-81800</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,91 +8819,92 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-64700</v>
+        <v>64700</v>
       </c>
       <c r="E96" s="3">
-        <v>-64700</v>
+        <v>64700</v>
       </c>
       <c r="F96" s="3">
-        <v>-57600</v>
+        <v>64700</v>
       </c>
       <c r="G96" s="3">
-        <v>-57600</v>
+        <v>57600</v>
       </c>
       <c r="H96" s="3">
-        <v>-57600</v>
+        <v>57600</v>
       </c>
       <c r="I96" s="3">
-        <v>-57500</v>
+        <v>57600</v>
       </c>
       <c r="J96" s="3">
+        <v>57500</v>
+      </c>
+      <c r="K96" s="3">
         <v>-50500</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-50400</v>
       </c>
       <c r="L96" s="3">
         <v>-50400</v>
       </c>
       <c r="M96" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="N96" s="3">
         <v>-50800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-46300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-46200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-46100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-46000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-41300</v>
       </c>
       <c r="S96" s="3">
         <v>-41300</v>
       </c>
       <c r="T96" s="3">
-        <v>-41200</v>
+        <v>-41300</v>
       </c>
       <c r="U96" s="3">
         <v>-41200</v>
       </c>
       <c r="V96" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="W96" s="3">
         <v>-32000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-31800</v>
       </c>
       <c r="Y96" s="3">
         <v>-31800</v>
       </c>
       <c r="Z96" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-32400</v>
       </c>
       <c r="AB96" s="3">
         <v>-32400</v>
       </c>
       <c r="AC96" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-32300</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-20700</v>
       </c>
       <c r="AE96" s="3">
         <v>-20700</v>
@@ -8679,16 +8913,19 @@
         <v>-20700</v>
       </c>
       <c r="AG96" s="3">
-        <v>-20600</v>
+        <v>-20700</v>
       </c>
       <c r="AH96" s="3">
         <v>-20600</v>
       </c>
       <c r="AI96" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-20700</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-476800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-334100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-417500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1062100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-47700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-102100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-215000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-74500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-130800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-183000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-187400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-131900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-320400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>575600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-84000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-454700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-141100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-430300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>486600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>280800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-16400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-25700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-165900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>330300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-261700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-28500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-27100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-286200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-75100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>51900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>98400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-97900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-2400</v>
+        <v>-12500</v>
       </c>
       <c r="E101" s="3">
-        <v>-7300</v>
+        <v>400</v>
       </c>
       <c r="F101" s="3">
-        <v>15300</v>
+        <v>5100</v>
       </c>
       <c r="G101" s="3">
-        <v>-12500</v>
+        <v>22200</v>
       </c>
       <c r="H101" s="3">
-        <v>400</v>
+        <v>-20500</v>
       </c>
       <c r="I101" s="3">
-        <v>5100</v>
+        <v>-18400</v>
       </c>
       <c r="J101" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K101" s="3">
         <v>22200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-20500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-18400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>13900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>11300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-12600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>12200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-12000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-25600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>13700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>6600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>16500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>20800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>6900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-21600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
         <v>22800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-36000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-432100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>236300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>205700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>54500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>35400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-38700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-32000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-733000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-89200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-92000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>173900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-122400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>860400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-342300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>167500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>199800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>14100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-164700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-39000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-89500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-90100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>219900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-53800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-147000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>271800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-10700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>AME</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1761600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1708600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1734800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1736200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1730900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1622800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1646100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1597100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1625700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1551800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1514600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1458500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1503700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1440700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1386300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1215700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1198900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1126900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1011900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1202200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1304800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1276600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1289400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1287700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1271300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1193000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1208900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1172600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1143100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1084800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1064600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1007700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>973000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1116900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1092800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1110400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1144700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1115900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1020900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1053200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1022500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1063700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1004600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>988200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>948800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>982400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>949400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>912700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>789400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>770000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>732700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>669200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>780900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>858200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>823300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>838200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>851300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>835300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>783000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>791200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>776800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>767000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>722100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>702200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>667400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>735600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>612700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>644700</v>
+      </c>
+      <c r="E10" s="3">
         <v>615800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>624400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>591500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>615000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>601900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>592900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>574600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>562000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>547200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>526400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>509700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>521300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>491300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>473600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>426300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>428900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>394200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>342700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>421300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>446600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>453300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>451200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>436400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>436000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>410000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>417700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>395800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>376100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>362700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>362400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>340300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>237400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>332300</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,13 +1165,14 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>371900</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1167,11 +1180,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>351700</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1393,8 +1412,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1402,8 +1421,8 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1411,20 +1430,20 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>-97100</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1441,8 +1460,8 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1465,35 +1484,38 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>95900</v>
+      </c>
+      <c r="E15" s="3">
         <v>90400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>98700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>98000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>91900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>81800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>81600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>82400</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1545,8 +1567,8 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>8</v>
+      <c r="AC15" s="3">
+        <v>0</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>8</v>
@@ -1566,11 +1588,14 @@
       <c r="AI15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AJ15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK15" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1263900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1270400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1296300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1330900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1253400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1194000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1237200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1205000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1227600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1167300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1149700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1105300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1142600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1103100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1069700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>922400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>900800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>856200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>784900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>829200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1007200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>975600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>994000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1004400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>989300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>927700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>938800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>914500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>913500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>854800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>835100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>790200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>799700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>743900</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>497700</v>
+      </c>
+      <c r="E18" s="3">
         <v>438100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>438600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>405200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>477500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>428900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>408900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>392100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>398100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>384500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>364900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>353200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>361100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>337600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>316600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>293300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>298100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>270700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>227000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>373000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>297600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>301000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>295400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>283300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>282000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>265300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>270100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>258100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>229600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>230000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>229500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>217500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>173300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>201100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,528 +1882,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-11300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>48500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-6200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4400</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-1900</v>
       </c>
       <c r="S20" s="3">
         <v>-1900</v>
       </c>
       <c r="T20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="U20" s="3">
         <v>-1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-1000</v>
       </c>
       <c r="AC20" s="3">
         <v>-1000</v>
       </c>
       <c r="AD20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-7800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-4400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>555400</v>
+      </c>
+      <c r="E21" s="3">
         <v>534300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>546300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>514600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>521000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>513700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>496700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>482500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>490000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>463500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>443900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>433900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>437400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>414800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>387400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>356000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>361000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>332300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>290500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>439900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>355100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>350800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>349200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>337100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>332700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>312500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>317900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>306300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>274000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>273800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>271800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>258500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>225600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E22" s="3">
         <v>25100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>30600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>35300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>24100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>18400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>23000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>19600</v>
-      </c>
-      <c r="O22" s="3">
-        <v>20500</v>
       </c>
       <c r="P22" s="3">
         <v>20500</v>
       </c>
       <c r="Q22" s="3">
+        <v>20500</v>
+      </c>
+      <c r="R22" s="3">
         <v>20400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>18900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>19500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>21200</v>
-      </c>
-      <c r="U22" s="3">
-        <v>22700</v>
       </c>
       <c r="V22" s="3">
         <v>22700</v>
       </c>
       <c r="W22" s="3">
+        <v>22700</v>
+      </c>
+      <c r="X22" s="3">
         <v>23000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>21300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>21500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>22700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>20300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>19400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>20800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>21700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>24300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>24700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>24600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>24500</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>23600</v>
       </c>
       <c r="AJ22" s="3">
         <v>23600</v>
       </c>
+      <c r="AK22" s="3">
+        <v>23600</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>444400</v>
+      </c>
+      <c r="E23" s="3">
         <v>418800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>417000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>381300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>416900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>413500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>396400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>379600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>378500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>367500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>346500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>336200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>339300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>319700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>291800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>272500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>276700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>248100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>206500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>351100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>268000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>274200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>270600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>256900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>258800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>244900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>248200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>235800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>197500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>204400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>203400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>191400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>145300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E24" s="3">
         <v>78600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>79300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>70400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>74100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>73100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>72100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>73900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>71400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>69900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>64100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>63800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>57600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>62200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>60100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>53200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>55700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>43500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>40200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>70500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>47200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>53500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>55100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>52700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>59100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>53700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>54400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>54500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>50600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>50900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>52900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>52500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>36100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>387300</v>
+      </c>
+      <c r="E26" s="3">
         <v>340200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>337700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>310900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>342900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>340400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>324200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>305700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>307100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>297600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>282400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>272400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>281700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>257500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>231700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>219200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>221000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>204600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>166200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>280600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>220800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>220700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>215500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>204300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>199700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>191200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>193900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>181300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>146900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>153500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>150500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>138900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>109100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>387300</v>
+      </c>
+      <c r="E27" s="3">
         <v>340200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>337700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>310900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>342900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>340400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>324200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>305700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>307100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>297600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>282400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>272400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>281700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>257500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>231700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>219200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>221000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>204600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>166200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>280600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>220800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>220700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>215500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>204300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>199700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>191200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>193900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>181300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>146900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>153500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>150500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>138900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>109100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2842,8 +2902,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2860,11 +2920,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>11800</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2872,11 +2932,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>91600</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-38100</v>
+      </c>
+      <c r="E32" s="3">
         <v>5800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>11300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-48500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>6200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4400</v>
-      </c>
-      <c r="R32" s="3">
-        <v>1900</v>
       </c>
       <c r="S32" s="3">
         <v>1900</v>
       </c>
       <c r="T32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U32" s="3">
         <v>1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2900</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>1000</v>
       </c>
       <c r="AC32" s="3">
         <v>1000</v>
       </c>
       <c r="AD32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE32" s="3">
         <v>600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>7800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>387300</v>
+      </c>
+      <c r="E33" s="3">
         <v>340200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>337700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>310900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>342900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>340400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>324200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>305700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>307100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>297600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>282400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>272400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>281700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>257500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>231700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>219200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>221000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>204600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>166200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>280600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>220800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>220700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>215500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>204300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>211500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>191200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>193900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>181300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>238500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>153500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>150500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>138900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>109100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>387300</v>
+      </c>
+      <c r="E35" s="3">
         <v>340200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>337700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>310900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>342900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>340400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>324200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>305700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>307100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>297600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>282400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>272400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>281700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>257500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>231700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>219200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>221000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>204600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>166200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>280600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>220800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>220700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>215500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>204300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>211500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>191200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>193900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>181300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>238500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>153500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>150500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>138900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>109100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E41" s="3">
         <v>396300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>396600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>373800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>409800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>841900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>605600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>399900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>345400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>309900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>348700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>340300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>346800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>358700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>390600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1123700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1212800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1304800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1131000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1253400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>393000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>735400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>567900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>368100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>354000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>518700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>557700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>556800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>646300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>736400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>516500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>570200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>717300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>445500</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,736 +3996,760 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>985900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1119700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1126100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1130800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1070200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1076600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1074400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1028900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1039100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>988100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>993000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>957200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>924500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>851400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>827900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>749900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>666400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>682900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>688000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>793000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>817800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>840000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>839600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>839500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>732800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>714900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>711000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>684600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>668200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>640800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>642300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>603900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>592300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>595100</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1021700</v>
+      </c>
+      <c r="E44" s="3">
         <v>1084600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1101700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1127300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1132500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1087600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1107800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1117100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1044300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1025100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>966600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>866500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>769200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>738700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>711600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>604300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>559200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>584800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>621500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>654300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>624600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>623700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>634100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>640600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>624700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>620100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>614400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>596300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>540500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>546900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>541200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>529900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>492100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>537200</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>221400</v>
+      </c>
+      <c r="E45" s="3">
         <v>133100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>142800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>143600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>212200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>112600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>111800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>120100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>99300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>109300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>103400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>108900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>88300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>113100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>111900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>95600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>84000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>70500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>76700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>73800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>190400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>73200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>85500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>76500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>124600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>144800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>135100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>122500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>79700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>100400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>89300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>83400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>126500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>119100</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2603000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2733700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2767200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2775500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2824700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3118700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2899600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2665900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2528100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2432600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2411600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2272800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2128800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2061800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2042100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2573500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2522500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2643000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2517100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2774500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2025800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2272200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2127200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1924600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1836100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1998600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2018100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1960200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1934700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2024500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1789300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1787400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1928200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1696900</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>143200</v>
+      </c>
+      <c r="E47" s="3">
         <v>10900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>12000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>12400</v>
       </c>
-      <c r="G47" s="3">
-        <v>11900</v>
-      </c>
       <c r="H47" s="3">
+        <v>150700</v>
+      </c>
+      <c r="I47" s="3">
         <v>11000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>382500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>405800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>399500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>387600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>375000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>325500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>322200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>297200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>292600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>281800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>289800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>280300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>279800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>257300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>269600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>262200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>256200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>256800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>244800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>240500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>239100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>159100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>155000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>152400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>146300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>175100</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1054300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1034000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1079000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1097300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1121000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>797100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>809200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>804700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>805900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>756100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>766000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>780300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>787100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>766600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>777500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>716000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>693800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>675400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>680800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>703300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>728600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>711600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>721200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>724900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>554100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>487400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>490100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>492400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>493300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>495000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>492500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>482900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>473200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>478600</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10471100</v>
+      </c>
+      <c r="E49" s="3">
         <v>10501300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10466600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10519300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10612900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8762900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8728900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8751600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8714600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8444400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8407900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8531300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8607400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8525900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8613500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6993300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6848600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6833200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6823500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6843800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6810400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5978600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5951700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5979800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6015800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5365200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5399400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5365300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5129000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5104700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5098200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4876000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4553000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4626400</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,35 +4959,38 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>281400</v>
+      </c>
+      <c r="E52" s="3">
         <v>487800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>470900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>460500</v>
       </c>
-      <c r="G52" s="3">
-        <v>378700</v>
-      </c>
       <c r="H52" s="3">
+        <v>239900</v>
+      </c>
+      <c r="I52" s="3">
         <v>403700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>391700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>383400</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -4947,8 +5066,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14631200</v>
+      </c>
+      <c r="E54" s="3">
         <v>14767600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14795900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14865000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15023500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13093400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12839900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12616000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12431100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12038900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11985000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11972000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11898200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11679700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11755300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10579900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10357500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10433400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10311200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10601900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9844600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9219700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9069600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>8891500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8662300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8108000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8152500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8058400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7796100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7783300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7535000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7298800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7100700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>6977100</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5360,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>523300</v>
+      </c>
+      <c r="E57" s="3">
         <v>511700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>510500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>517400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>516600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>486600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>487700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>526100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>497100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>524300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>540700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>504200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>470300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>446400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>446500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>397100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>360400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>324800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>337500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>373900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>377200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>381900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>390400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>405600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>399600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>389100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>394300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>382300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>437300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>409400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>405900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>382800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>369500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>345500</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>709100</v>
+      </c>
+      <c r="E58" s="3">
         <v>625400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>886700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1115500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1479000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>349400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>51600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>116500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>226100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>272000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>354800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>331400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>315100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>415700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>700000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>94700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>132300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>505000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>115900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>510800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>497400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>199500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>98400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>104200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>358900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>68700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>307700</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>308100</v>
       </c>
       <c r="AE58" s="3">
         <v>308100</v>
       </c>
       <c r="AF58" s="3">
+        <v>308100</v>
+      </c>
+      <c r="AG58" s="3">
         <v>509600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>272600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>338000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>278900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>613700</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>663600</v>
+      </c>
+      <c r="E59" s="3">
         <v>519800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>461800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>513900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>658600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>456100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>459600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>511800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>841000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>795100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>737600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>755100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>778000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>771800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>711100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>646700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>583300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>573600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>564100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>593000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>551200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>529000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>489800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>497400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>500300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>512000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>480600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>469500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>393200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>351400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>316700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>296000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>276000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>257600</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2098600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1966900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2203000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2502500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2882600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1673700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1341200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1452700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1564200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1591400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1633000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1590700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1563300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1633800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1857600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1138500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1075900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1403500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1017500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1477700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1425900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1110500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>978600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1007200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1258700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>969900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1182500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1159900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1138700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1270300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>995100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1016800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>924400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1216700</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1615400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1931900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1996000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2051600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2077900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1980600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2315900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2300900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2158900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2085400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2147400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2204600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2229100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2238900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2262100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2256900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2281400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2295800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2753300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2741800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2271300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2229300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2368700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2368200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2273800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1832500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1838200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1897600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1866200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1920900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2128800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2076600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2062600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>393800</v>
+      </c>
+      <c r="E62" s="3">
         <v>480700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>477800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>458600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>438900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>407600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>387600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>380300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1231500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1229500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1254500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1245000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1233800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1248600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1292200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1063800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1050800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1029900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1054000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1056500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1031900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1014000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1055600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1059400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>887800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>793700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>793600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>796400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>763600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>825900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>818800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>801200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>857100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>846400</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4975900</v>
+      </c>
+      <c r="E66" s="3">
         <v>5217400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5543500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5896800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6293300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4750900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4758500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4858900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4954600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4906300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5034900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5040300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5026300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5121300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5412000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4459100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4408100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4729200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4824700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5275900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4729100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4353700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4402800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4434900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4420400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3596100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3814400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3854000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3768400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4017100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3942800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3894600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3844200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3603900</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11057700</v>
+      </c>
+      <c r="E72" s="3">
         <v>10735100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10459600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10186600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9940300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9655100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9372400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9105700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8857500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8600900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8353700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8121800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7900100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7664700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7453400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7267900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7094700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6915000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6751700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6626700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6387600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6198800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6010000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5826300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5653800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5474100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5315200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5153700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5002400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4784600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4651800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4522000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4403700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4315100</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9655300</v>
+      </c>
+      <c r="E76" s="3">
         <v>9550200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9252400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8968200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8730200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8342500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8081400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7757100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7476500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7132700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6950100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6931700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6871900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6558400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6343300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6120700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5949300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5704200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5486400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5326000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5115500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4866000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4666800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4456600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4241900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4511900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4338100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4204400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4027600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3766200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3592200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3404200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3256500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3373200</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>387300</v>
+      </c>
+      <c r="E81" s="3">
         <v>340200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>337700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>310900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>342900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>340400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>324200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>305700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>307100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>297600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>282400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>272400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>281700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>257500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>231700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>219200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>221000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>204600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>166200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>280600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>220800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>220700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>215500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>204300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>211500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>191200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>193900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>181300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>238500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>153500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>150500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>138900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>109100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>91900</v>
+      </c>
+      <c r="E83" s="3">
         <v>81800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>81600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>82400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>88500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>75800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>77100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>78100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>88500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>75800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>77100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>78100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>77600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>74700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>75200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>64600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>64900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>63000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>61300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>66100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>64100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>55300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>57200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>57500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>53600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>48100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>48900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>48800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>52200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>44600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>43800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>42500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>56700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>550000</v>
+      </c>
+      <c r="E89" s="3">
         <v>487200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>381400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>410200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>540700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>472900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>335200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>386500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>385000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>327100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>235900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>201300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>281900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>307100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>287000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>284400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>385900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>309700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>314600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>270800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>342200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>329600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>246300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>196300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>296200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>248800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>203100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>177400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>252900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>239000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>199000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>142400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>247300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>169000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-51700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-26300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-21400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-27700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-59700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-28700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-27800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-58200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-28300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-26200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-26400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-43400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-26200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-23500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-17500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-37000</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-10100</v>
       </c>
       <c r="U91" s="3">
         <v>-10100</v>
       </c>
       <c r="V91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="W91" s="3">
         <v>-16900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-40800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-18200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-21900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-21400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-34600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-16300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-12300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-29400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-13400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-175300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-26000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-22100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2050100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-176300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-27800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-122200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-297200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-214500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-26200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-160700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1597600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-284500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-37100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>115600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-977600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-133700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-21900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-17800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-785800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-22500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-148200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-253600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-63400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-15700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-198400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-348300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-52400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-81800</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8835,7 +9068,7 @@
         <v>64700</v>
       </c>
       <c r="G96" s="3">
-        <v>57600</v>
+        <v>64700</v>
       </c>
       <c r="H96" s="3">
         <v>57600</v>
@@ -8844,70 +9077,70 @@
         <v>57600</v>
       </c>
       <c r="J96" s="3">
+        <v>57600</v>
+      </c>
+      <c r="K96" s="3">
         <v>57500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-50500</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-50400</v>
       </c>
       <c r="M96" s="3">
         <v>-50400</v>
       </c>
       <c r="N96" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="O96" s="3">
         <v>-50800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-46300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-46200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-46100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-46000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-41300</v>
       </c>
       <c r="T96" s="3">
         <v>-41300</v>
       </c>
       <c r="U96" s="3">
-        <v>-41200</v>
+        <v>-41300</v>
       </c>
       <c r="V96" s="3">
         <v>-41200</v>
       </c>
       <c r="W96" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="X96" s="3">
         <v>-32000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-31800</v>
       </c>
       <c r="Z96" s="3">
         <v>-31800</v>
       </c>
       <c r="AA96" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-32400</v>
       </c>
       <c r="AC96" s="3">
         <v>-32400</v>
       </c>
       <c r="AD96" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-32300</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-20700</v>
       </c>
       <c r="AF96" s="3">
         <v>-20700</v>
@@ -8916,16 +9149,19 @@
         <v>-20700</v>
       </c>
       <c r="AH96" s="3">
-        <v>-20600</v>
+        <v>-20700</v>
       </c>
       <c r="AI96" s="3">
         <v>-20600</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-20700</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-374000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-476800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-334100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-417500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1062100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-47700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-102100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-215000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-74500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-130800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-183000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-187400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-131900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-320400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>575600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-84000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-454700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-141100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-430300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>486600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>280800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-16400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-25700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-165900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>330300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-261700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-28500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-27100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-286200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-75100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>51900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>98400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-97900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-12500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>22200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-20500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-18400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>22200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-20500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-18400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>13900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>11300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>4000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-12600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>12200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-25600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>13700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>6600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>16500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>20800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>6900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-21600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>22800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-36000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-432100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>236300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>205700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>54500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>35400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-38700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-32000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-733000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-89200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-92000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>173900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-122400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>860400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-342300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>167500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>199800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>14100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-164700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-39000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-89500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-90100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>219900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-53800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-147000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>271800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-10700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>AME</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1732000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1761600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1708600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1734800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1736200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1730900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1622800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1646100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1597100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1625700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1551800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1514600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1458500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1503700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1440700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1386300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1215700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1198900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1126900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1011900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1202200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1304800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1276600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1289400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1287700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1271300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1193000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1208900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1172600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1143100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1084800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1064600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1007700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>973000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1107000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1116900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1092800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1110400</v>
       </c>
-      <c r="G9" s="3">
-        <v>1144700</v>
-      </c>
       <c r="H9" s="3">
+        <v>1115500</v>
+      </c>
+      <c r="I9" s="3">
         <v>1115900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1020900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1053200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1022500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1063700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1004600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>988200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>948800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>982400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>949400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>912700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>789400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>770000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>732700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>669200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>780900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>858200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>823300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>838200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>851300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>835300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>783000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>791200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>776800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>767000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>722100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>702200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>667400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>735600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>612700</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>625000</v>
+      </c>
+      <c r="E10" s="3">
         <v>644700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>615800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>624400</v>
       </c>
-      <c r="G10" s="3">
-        <v>591500</v>
-      </c>
       <c r="H10" s="3">
+        <v>620700</v>
+      </c>
+      <c r="I10" s="3">
         <v>615000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>601900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>592900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>574600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>562000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>547200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>526400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>509700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>521300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>491300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>473600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>426300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>428900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>394200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>342700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>421300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>446600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>453300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>451200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>436400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>436000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>410000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>417700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>395800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>376100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>362700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>362400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>340300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>237400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>332300</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,16 +1179,17 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>371900</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1183,11 +1197,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>351700</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1397,8 +1417,8 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>29200</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1415,8 +1435,8 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1424,8 +1444,8 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1433,20 +1453,20 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>-97100</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1463,8 +1483,8 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1487,38 +1507,41 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>106400</v>
+      </c>
+      <c r="E15" s="3">
         <v>95900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>90400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>98700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>98000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>91900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>81800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>81600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>82400</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1570,8 +1593,8 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>8</v>
+      <c r="AD15" s="3">
+        <v>0</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>8</v>
@@ -1591,11 +1614,14 @@
       <c r="AJ15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AK15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL15" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1287600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1263900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1270400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1296300</v>
       </c>
-      <c r="G17" s="3">
-        <v>1330900</v>
-      </c>
       <c r="H17" s="3">
+        <v>1301700</v>
+      </c>
+      <c r="I17" s="3">
         <v>1253400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1194000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1237200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1205000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1227600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1167300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1149700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1105300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1142600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1103100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1069700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>922400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>900800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>856200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>784900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>829200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1007200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>975600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>994000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1004400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>989300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>927700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>938800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>914500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>913500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>854800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>835100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>790200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>799700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>743900</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>444400</v>
+      </c>
+      <c r="E18" s="3">
         <v>497700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>438100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>438600</v>
       </c>
-      <c r="G18" s="3">
-        <v>405200</v>
-      </c>
       <c r="H18" s="3">
+        <v>434400</v>
+      </c>
+      <c r="I18" s="3">
         <v>477500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>428900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>408900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>392100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>398100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>384500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>364900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>353200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>361100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>337600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>316600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>293300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>298100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>270700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>227000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>373000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>297600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>301000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>295400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>283300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>282000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>265300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>270100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>258100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>229600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>230000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>229500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>217500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>173300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>201100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,543 +1916,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E20" s="3">
         <v>38100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-9100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-11300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>48500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4400</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-1900</v>
       </c>
       <c r="T20" s="3">
         <v>-1900</v>
       </c>
       <c r="U20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="V20" s="3">
         <v>-1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-1000</v>
       </c>
       <c r="AD20" s="3">
         <v>-1000</v>
       </c>
       <c r="AE20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-7800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-4400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>559600</v>
+      </c>
+      <c r="E21" s="3">
         <v>555400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>534300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>546300</v>
       </c>
-      <c r="G21" s="3">
-        <v>514600</v>
-      </c>
       <c r="H21" s="3">
+        <v>543800</v>
+      </c>
+      <c r="I21" s="3">
         <v>521000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>513700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>496700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>482500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>490000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>463500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>443900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>433900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>437400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>414800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>387400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>356000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>361000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>332300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>290500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>439900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>355100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>350800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>349200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>337100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>332700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>312500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>317900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>306300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>274000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>273800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>271800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>258500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>225600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E22" s="3">
         <v>22000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>25100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>30600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>35300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>24100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>18700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>23000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>19600</v>
-      </c>
-      <c r="P22" s="3">
-        <v>20500</v>
       </c>
       <c r="Q22" s="3">
         <v>20500</v>
       </c>
       <c r="R22" s="3">
+        <v>20500</v>
+      </c>
+      <c r="S22" s="3">
         <v>20400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>18900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>21200</v>
-      </c>
-      <c r="V22" s="3">
-        <v>22700</v>
       </c>
       <c r="W22" s="3">
         <v>22700</v>
       </c>
       <c r="X22" s="3">
+        <v>22700</v>
+      </c>
+      <c r="Y22" s="3">
         <v>23000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>21300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>21500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>22700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>20300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>19400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>20800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>21700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>24300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>24700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>24600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>24500</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>23600</v>
       </c>
       <c r="AK22" s="3">
         <v>23600</v>
       </c>
+      <c r="AL22" s="3">
+        <v>23600</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>434200</v>
+      </c>
+      <c r="E23" s="3">
         <v>444400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>418800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>417000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>381300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>416900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>413500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>396400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>379600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>378500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>367500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>346500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>336200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>339300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>319700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>291800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>272500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>276700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>248100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>206500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>351100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>268000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>274200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>270600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>256900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>258800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>244900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>248200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>235800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>197500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>204400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>203400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>191400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>145300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E24" s="3">
         <v>57100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>78600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>79300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>70400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>74100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>73100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>72100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>73900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>71400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>69900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>64100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>63800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>57600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>62200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>60100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>53200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>55700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>43500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>40200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>70500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>47200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>53500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>55100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>52700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>59100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>53700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>54400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>54500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>50600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>50900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>52900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>52500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>36100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>351800</v>
+      </c>
+      <c r="E26" s="3">
         <v>387300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>340200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>337700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>310900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>342900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>340400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>324200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>305700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>307100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>297600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>282400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>272400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>281700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>257500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>231700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>219200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>221000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>204600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>166200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>280600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>220800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>220700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>215500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>204300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>199700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>191200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>193900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>181300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>146900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>153500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>150500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>138900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>109100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>351800</v>
+      </c>
+      <c r="E27" s="3">
         <v>387300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>340200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>337700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>310900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>342900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>340400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>324200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>305700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>307100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>297600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>282400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>272400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>281700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>257500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>231700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>219200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>221000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>204600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>166200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>280600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>220800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>220700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>215500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>204300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>199700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>191200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>193900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>181300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>146900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>153500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>150500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>138900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>109100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2905,8 +2966,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2923,11 +2984,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>11800</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2935,11 +2996,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>91600</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3234,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-38100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>9100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>11300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-48500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4400</v>
-      </c>
-      <c r="S32" s="3">
-        <v>1900</v>
       </c>
       <c r="T32" s="3">
         <v>1900</v>
       </c>
       <c r="U32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="V32" s="3">
         <v>1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2900</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>1000</v>
       </c>
       <c r="AD32" s="3">
         <v>1000</v>
       </c>
       <c r="AE32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF32" s="3">
         <v>600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>7800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>4400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>351800</v>
+      </c>
+      <c r="E33" s="3">
         <v>387300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>340200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>337700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>310900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>342900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>340400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>324200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>305700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>307100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>297600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>282400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>272400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>281700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>257500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>231700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>219200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>221000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>204600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>166200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>280600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>220800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>220700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>215500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>204300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>211500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>191200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>193900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>181300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>238500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>153500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>150500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>138900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>109100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>351800</v>
+      </c>
+      <c r="E35" s="3">
         <v>387300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>340200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>337700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>310900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>342900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>340400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>324200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>305700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>307100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>297600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>282400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>272400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>281700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>257500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>231700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>219200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>221000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>204600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>166200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>280600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>220800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>220700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>215500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>204300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>211500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>191200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>193900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>181300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>238500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>153500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>150500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>138900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>109100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>399000</v>
+      </c>
+      <c r="E41" s="3">
         <v>374000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>396300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>396600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>373800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>409800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>841900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>605600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>399900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>345400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>309900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>348700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>340300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>346800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>358700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>390600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1123700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1212800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1304800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1131000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1253400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>393000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>735400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>567900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>368100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>354000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>518700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>557700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>556800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>646300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>736400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>516500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>570200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>717300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>445500</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3999,757 +4089,781 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>32154400</v>
+      </c>
+      <c r="E43" s="3">
         <v>985900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1119700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1126100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1130800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1070200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1076600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1074400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1028900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1039100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>988100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>993000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>957200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>924500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>851400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>827900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>749900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>666400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>682900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>688000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>793000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>817800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>840000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>839600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>839500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>732800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>714900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>711000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>684600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>668200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>640800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>642300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>603900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>592300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>595100</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1069500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1021700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1084600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1101700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1127300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1132500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1087600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1107800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1117100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1044300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1025100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>966600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>866500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>769200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>738700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>711600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>604300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>559200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>584800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>621500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>654300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>624600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>623700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>634100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>640600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>624700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>620100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>614400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>596300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>540500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>546900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>541200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>529900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>492100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>537200</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>221400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>133100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>142800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>143600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>212200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>112600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>111800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>120100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>99300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>109300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>103400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>108900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>88300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>113100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>111900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>95600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>84000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>70500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>76700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>73800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>190400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>73200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>85500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>76500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>124600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>144800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>135100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>122500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>79700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>100400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>89300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>83400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>126500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>119100</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2760800</v>
+      </c>
+      <c r="E46" s="3">
         <v>2603000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2733700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2767200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2775500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2824700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3118700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2899600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2665900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2528100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2432600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2411600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2272800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2128800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2061800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2042100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2573500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2522500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2643000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2517100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2774500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2025800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2272200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2127200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1924600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1836100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1998600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2018100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1960200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1934700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2024500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1789300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1787400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1928200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1696900</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E47" s="3">
         <v>143200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>12000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>12400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>150700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>382500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>405800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>399500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>387600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>375000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>325500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>322200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>297200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>292600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>281800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>289800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>280300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>279800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>257300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>269600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>262200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>256200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>256800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>244800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>240500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>239100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>159100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>155000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>152400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>146300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>175100</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1059000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1054300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1034000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1079000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1097300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1121000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>797100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>809200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>804700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>805900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>756100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>766000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>780300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>787100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>766600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>777500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>716000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>693800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>675400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>680800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>703300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>728600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>711600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>721200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>724900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>554100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>487400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>490100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>492400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>493300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>495000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>492500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>482900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>473200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>478600</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10548000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10471100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10501300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10466600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10519300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10612900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8762900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8728900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8751600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8714600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8444400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8407900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8531300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8607400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8525900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8613500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6993300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6848600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6833200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6823500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6843800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6810400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5978600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5951700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5979800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>6015800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5365200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5399400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5365300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5129000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5104700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5098200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4876000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4553000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4626400</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,38 +5079,41 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>499900</v>
+      </c>
+      <c r="E52" s="3">
         <v>281400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>487800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>470900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>460500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>239900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>403700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>391700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>383400</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -5069,8 +5189,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14877100</v>
+      </c>
+      <c r="E54" s="3">
         <v>14631200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14767600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14795900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14865000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15023500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13093400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12839900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12616000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12431100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12038900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11985000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11972000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11898200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11679700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11755300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10579900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10357500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10433400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10311200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10601900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9844600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9219700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9069600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8891500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8662300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8108000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8152500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8058400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7796100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7783300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7535000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7298800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>7100700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>6977100</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,650 +5491,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>534400</v>
+      </c>
+      <c r="E57" s="3">
         <v>523300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>511700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>510500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>517400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>516600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>486600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>487700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>526100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>497100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>524300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>540700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>504200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>470300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>446400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>446500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>397100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>360400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>324800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>337500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>373900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>377200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>381900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>390400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>405600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>399600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>389100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>394300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>382300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>437300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>409400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>405900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>382800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>369500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>345500</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>527900</v>
+      </c>
+      <c r="E58" s="3">
         <v>709100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>625400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>886700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1115500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1479000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>349400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>51600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>116500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>226100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>272000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>354800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>331400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>315100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>415700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>700000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>94700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>132300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>505000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>115900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>510800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>497400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>199500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>98400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>104200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>358900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>68700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>307700</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>308100</v>
       </c>
       <c r="AF58" s="3">
         <v>308100</v>
       </c>
       <c r="AG58" s="3">
+        <v>308100</v>
+      </c>
+      <c r="AH58" s="3">
         <v>509600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>272600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>338000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>278900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>613700</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>550000</v>
+      </c>
+      <c r="E59" s="3">
         <v>663600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>519800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>461800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>513900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>658600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>456100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>459600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>511800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>841000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>795100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>737600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>755100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>778000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>771800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>711100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>646700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>583300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>573600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>564100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>593000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>551200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>529000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>489800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>497400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>500300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>512000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>480600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>469500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>393200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>351400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>316700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>296000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>276000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>257600</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1962600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2098600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1966900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2203000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2502500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2882600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1673700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1341200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1452700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1564200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1591400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1633000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1590700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1563300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1633800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1857600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1138500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1075900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1403500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1017500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1477700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1425900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1110500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>978600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1007200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1258700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>969900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1182500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1159900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1138700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1270300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>995100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1016800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>924400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1216700</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1641700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1615400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1931900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1996000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2051600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2077900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1980600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2315900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2300900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2158900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2085400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2147400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2204600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2229100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2238900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2262100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2256900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2281400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2295800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2753300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2741800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2271300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2229300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2368700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2368200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2273800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1832500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1838200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1897600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1866200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1920900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2128800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2076600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2062600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>418600</v>
+      </c>
+      <c r="E62" s="3">
         <v>393800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>480700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>477800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>458600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>438900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>407600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>387600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>380300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1231500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1229500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1254500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1245000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1233800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1248600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1292200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1063800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1050800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1029900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1054000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1056500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1031900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1014000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1055600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1059400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>887800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>793700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>793600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>796400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>763600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>825900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>818800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>801200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>857100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>846400</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4907200</v>
+      </c>
+      <c r="E66" s="3">
         <v>4975900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5217400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5543500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5896800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6293300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4750900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4758500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4858900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4954600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4906300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5034900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5040300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5026300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5121300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5412000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4459100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4408100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4729200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4824700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5275900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4729100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4353700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4402800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4434900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4420400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3596100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3814400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3854000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3768400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4017100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3942800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3894600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3844200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3603900</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11338000</v>
+      </c>
+      <c r="E72" s="3">
         <v>11057700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10735100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10459600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10186600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9940300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9655100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9372400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9105700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8857500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8600900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8353700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8121800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7900100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7664700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7453400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7267900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7094700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6915000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6751700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6626700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6387600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6198800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6010000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5826300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5653800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5474100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5315200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5153700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5002400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4784600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4651800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4522000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4403700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4315100</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9969900</v>
+      </c>
+      <c r="E76" s="3">
         <v>9655300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9550200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9252400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8968200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8730200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8342500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8081400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7757100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7476500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7132700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6950100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6931700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6871900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6558400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6343300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6120700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5949300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5704200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5486400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5326000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5115500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4866000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4666800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4456600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4241900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4511900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4338100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4204400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4027600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3766200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3592200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3404200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3256500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3373200</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>351800</v>
+      </c>
+      <c r="E81" s="3">
         <v>387300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>340200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>337700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>310900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>342900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>340400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>324200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>305700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>307100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>297600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>282400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>272400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>281700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>257500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>231700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>219200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>221000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>204600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>166200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>280600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>220800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>220700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>215500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>204300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>211500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>191200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>193900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>181300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>238500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>153500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>150500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>138900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>109100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E83" s="3">
         <v>91900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>81800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>81600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>82400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>88500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>75800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>77100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>78100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>88500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>75800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>77100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>78100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>77600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>74700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>75200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>64600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>64900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>63000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>61300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>66100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>64100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>55300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>57200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>57500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>53600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>48100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>48900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>48800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>52200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>44600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>43800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>42500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>56700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>417500</v>
+      </c>
+      <c r="E89" s="3">
         <v>550000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>487200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>381400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>410200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>540700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>472900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>335200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>386500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>385000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>327100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>235900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>201300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>281900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>307100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>287000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>284400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>385900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>309700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>314600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>270800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>342200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>329600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>246300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>196300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>296200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>248800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>203100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>177400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>252900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>239000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>199000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>142400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>247300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>169000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-51700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-26300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-21400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-27700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-59700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-28700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-27800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-58200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-28300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-26200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-26400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-43400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-26200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-23500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-17500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-37000</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-10100</v>
       </c>
       <c r="V91" s="3">
         <v>-10100</v>
       </c>
       <c r="W91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="X91" s="3">
         <v>-16900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-40800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-18200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-21900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-21400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-34600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-16300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-12300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-29400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-13400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-125700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-175300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-26000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-22100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2050100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-176300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-122200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-297200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-214500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-26200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-14900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-160700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1597600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-284500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-37100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-10800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>115600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-977600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-133700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-21900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-17800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-785800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-22500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-148200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-253600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-63400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-15700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-198400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-348300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-52400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-81800</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,13 +9286,14 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>64700</v>
+        <v>71500</v>
       </c>
       <c r="E96" s="3">
         <v>64700</v>
@@ -9071,7 +9305,7 @@
         <v>64700</v>
       </c>
       <c r="H96" s="3">
-        <v>57600</v>
+        <v>64700</v>
       </c>
       <c r="I96" s="3">
         <v>57600</v>
@@ -9080,70 +9314,70 @@
         <v>57600</v>
       </c>
       <c r="K96" s="3">
+        <v>57600</v>
+      </c>
+      <c r="L96" s="3">
         <v>57500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-50500</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-50400</v>
       </c>
       <c r="N96" s="3">
         <v>-50400</v>
       </c>
       <c r="O96" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="P96" s="3">
         <v>-50800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-46300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-46200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-46100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-46000</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-41300</v>
       </c>
       <c r="U96" s="3">
         <v>-41300</v>
       </c>
       <c r="V96" s="3">
-        <v>-41200</v>
+        <v>-41300</v>
       </c>
       <c r="W96" s="3">
         <v>-41200</v>
       </c>
       <c r="X96" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-32000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-31800</v>
       </c>
       <c r="AA96" s="3">
         <v>-31800</v>
       </c>
       <c r="AB96" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-32400</v>
       </c>
       <c r="AD96" s="3">
         <v>-32400</v>
       </c>
       <c r="AE96" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-32300</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-20700</v>
       </c>
       <c r="AG96" s="3">
         <v>-20700</v>
@@ -9152,16 +9386,19 @@
         <v>-20700</v>
       </c>
       <c r="AI96" s="3">
-        <v>-20600</v>
+        <v>-20700</v>
       </c>
       <c r="AJ96" s="3">
         <v>-20600</v>
       </c>
       <c r="AK96" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-20700</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-277700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-374000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-476800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-334100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-417500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1062100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-47700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-102100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-215000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-74500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-130800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-183000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-187400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-131900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-320400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>575600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-84000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-454700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-141100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-430300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>486600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>280800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-16400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-25700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-165900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>330300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-261700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-28500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-27100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-286200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-75100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>51900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>98400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-97900</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E101" s="3">
         <v>15300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-12500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>5100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>22200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-20500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-18400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>22200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-20500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-18400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-5100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>13900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>11300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>4000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-12600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>12200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-25600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>13700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>6600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>16500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>20800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>6900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-21600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-22300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>22800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-36000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-432100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>236300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>205700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>54500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>35400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-38700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-32000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-733000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-89200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-92000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>173900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-122400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>860400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-342300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>167500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>199800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>14100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-164700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-39000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-89500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-90100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>219900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-53800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-147000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>271800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-10700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>AME</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1778100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1732000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1761600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1708600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1734800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1736200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1730900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1622800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1646100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1597100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1625700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1551800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1514600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1458500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1503700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1440700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1386300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1215700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1198900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1126900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1011900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1202200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1304800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1276600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1289400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1287700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1271300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1193000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1208900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1172600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1143100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1084800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1064600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1007700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>973000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1142200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1107000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1116900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1092800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1110400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1115500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1115900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1020900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1053200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1022500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1063700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1004600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>988200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>948800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>982400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>949400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>912700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>789400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>770000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>732700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>669200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>780900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>858200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>823300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>838200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>851300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>835300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>783000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>791200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>776800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>767000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>722100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>702200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>667400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>735600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>612700</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>635900</v>
+      </c>
+      <c r="E10" s="3">
         <v>625000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>644700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>615800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>624400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>620700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>615000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>601900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>592900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>574600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>562000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>547200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>526400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>509700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>521300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>491300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>473600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>426300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>428900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>394200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>342700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>421300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>446600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>453300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>451200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>436400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>436000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>410000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>417700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>395800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>376100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>362700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>362400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>340300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>237400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>332300</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,19 +1193,20 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>371900</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1200,11 +1214,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>351700</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1417,11 +1437,11 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>29200</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1438,8 +1458,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1447,8 +1467,8 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1456,20 +1476,20 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-97100</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
@@ -1486,8 +1506,8 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1510,41 +1530,44 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>107700</v>
+      </c>
+      <c r="E15" s="3">
         <v>106400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>95900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>90400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>98700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>98000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>91900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>81800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>81600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>82400</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1596,8 +1619,8 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>8</v>
+      <c r="AE15" s="3">
+        <v>0</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>8</v>
@@ -1617,11 +1640,14 @@
       <c r="AK15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AL15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM15" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1325000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1287600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1263900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1270400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1296300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1301700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1253400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1194000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1237200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1205000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1227600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1167300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1149700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1105300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1142600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1103100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1069700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>922400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>900800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>856200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>784900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>829200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1007200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>975600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>994000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1004400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>989300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>927700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>938800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>914500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>913500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>854800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>835100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>790200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>799700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>743900</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>453100</v>
+      </c>
+      <c r="E18" s="3">
         <v>444400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>497700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>438100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>438600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>434400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>477500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>428900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>408900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>392100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>398100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>384500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>364900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>353200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>361100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>337600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>316600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>293300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>298100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>270700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>227000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>373000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>297600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>301000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>295400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>283300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>282000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>265300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>270100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>258100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>229600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>230000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>229500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>217500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>173300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>201100</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,558 +1950,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-8800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>38100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-11300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>48500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4400</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-1900</v>
       </c>
       <c r="U20" s="3">
         <v>-1900</v>
       </c>
       <c r="V20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="W20" s="3">
         <v>-1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-1000</v>
       </c>
       <c r="AE20" s="3">
         <v>-1000</v>
       </c>
       <c r="AF20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-7800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-4400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>566700</v>
+      </c>
+      <c r="E21" s="3">
         <v>559600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>555400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>534300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>546300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>543800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>521000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>513700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>496700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>482500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>490000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>463500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>443900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>433900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>437400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>414800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>387400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>356000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>361000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>332300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>290500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>439900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>355100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>350800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>349200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>337100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>332700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>312500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>317900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>306300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>274000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>273800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>271800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>258500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>225600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E22" s="3">
         <v>19000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>22000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>25100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>30600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>35300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>24100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>18400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>18700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>23000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>19600</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>20500</v>
       </c>
       <c r="R22" s="3">
         <v>20500</v>
       </c>
       <c r="S22" s="3">
+        <v>20500</v>
+      </c>
+      <c r="T22" s="3">
         <v>20400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>18900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>21200</v>
-      </c>
-      <c r="W22" s="3">
-        <v>22700</v>
       </c>
       <c r="X22" s="3">
         <v>22700</v>
       </c>
       <c r="Y22" s="3">
+        <v>22700</v>
+      </c>
+      <c r="Z22" s="3">
         <v>23000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>21300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>21500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>22700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>20300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>19400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>20800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>21700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>24300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>24700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>24600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>24500</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>23600</v>
       </c>
       <c r="AL22" s="3">
         <v>23600</v>
       </c>
+      <c r="AM22" s="3">
+        <v>23600</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>442200</v>
+      </c>
+      <c r="E23" s="3">
         <v>434200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>444400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>418800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>417000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>381300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>416900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>413500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>396400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>379600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>378500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>367500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>346500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>336200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>339300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>319700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>291800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>272500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>276700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>248100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>206500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>351100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>268000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>274200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>270600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>256900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>258800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>244900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>248200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>235800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>197500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>204400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>203400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>191400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>145300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>83800</v>
+      </c>
+      <c r="E24" s="3">
         <v>82500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>57100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>78600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>79300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>70400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>74100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>73100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>72100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>73900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>71400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>69900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>64100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>63800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>57600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>62200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>60100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>53200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>55700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>43500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>40200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>70500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>47200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>53500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>55100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>52700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>59100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>53700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>54400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>54500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>50600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>50900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>52900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>52500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>36100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>358400</v>
+      </c>
+      <c r="E26" s="3">
         <v>351800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>387300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>340200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>337700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>310900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>342900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>340400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>324200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>305700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>307100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>297600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>282400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>272400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>281700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>257500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>231700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>219200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>221000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>204600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>166200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>280600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>220800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>220700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>215500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>204300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>199700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>191200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>193900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>181300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>146900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>153500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>150500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>138900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>109100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>358400</v>
+      </c>
+      <c r="E27" s="3">
         <v>351800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>387300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>340200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>337700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>310900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>342900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>340400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>324200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>305700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>307100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>297600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>282400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>272400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>281700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>257500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>231700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>219200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>221000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>204600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>166200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>280600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>220800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>220700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>215500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>204300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>199700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>191200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>193900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>181300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>146900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>153500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>150500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>138900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>109100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2969,8 +3030,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2987,11 +3048,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>11800</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2999,11 +3060,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>91600</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E32" s="3">
         <v>8800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-38100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>11300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-48500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4400</v>
-      </c>
-      <c r="T32" s="3">
-        <v>1900</v>
       </c>
       <c r="U32" s="3">
         <v>1900</v>
       </c>
       <c r="V32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="W32" s="3">
         <v>1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2900</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>1000</v>
       </c>
       <c r="AE32" s="3">
         <v>1000</v>
       </c>
       <c r="AF32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG32" s="3">
         <v>600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>7800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>4400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>358400</v>
+      </c>
+      <c r="E33" s="3">
         <v>351800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>387300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>340200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>337700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>310900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>342900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>340400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>324200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>305700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>307100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>297600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>282400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>272400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>281700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>257500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>231700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>219200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>221000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>204600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>166200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>280600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>220800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>220700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>215500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>204300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>211500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>191200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>193900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>181300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>238500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>153500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>150500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>138900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>109100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>358400</v>
+      </c>
+      <c r="E35" s="3">
         <v>351800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>387300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>340200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>337700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>310900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>342900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>340400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>324200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>305700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>307100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>297600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>282400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>272400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>281700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>257500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>231700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>219200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>221000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>204600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>166200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>280600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>220800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>220700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>215500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>204300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>211500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>191200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>193900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>181300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>238500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>153500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>150500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>138900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>109100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>619700</v>
+      </c>
+      <c r="E41" s="3">
         <v>399000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>374000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>396300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>396600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>373800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>409800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>841900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>605600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>399900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>345400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>309900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>348700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>340300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>346800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>358700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>390600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1123700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1212800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1304800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1131000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1253400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>393000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>735400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>567900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>368100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>354000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>518700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>557700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>556800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>646300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>736400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>516500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>570200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>717300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>445500</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4092,778 +4182,802 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>32154400</v>
+        <v>1181400</v>
       </c>
       <c r="E43" s="3">
+        <v>1154400</v>
+      </c>
+      <c r="F43" s="3">
         <v>985900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1119700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1126100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1130800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1070200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1076600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1074400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1028900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1039100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>988100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>993000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>957200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>924500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>851400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>827900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>749900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>666400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>682900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>688000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>793000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>817800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>840000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>839600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>839500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>732800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>714900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>711000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>684600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>668200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>640800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>642300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>603900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>592300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>595100</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1110500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1069500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1021700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1084600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1101700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1127300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1132500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1087600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1107800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1117100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1044300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1025100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>966600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>866500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>769200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>738700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>711600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>604300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>559200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>584800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>621500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>654300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>624600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>623700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>634100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>640600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>624700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>620100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>614400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>596300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>540500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>546900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>541200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>529900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>492100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>537200</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>140200</v>
       </c>
       <c r="E45" s="3">
+        <v>137900</v>
+      </c>
+      <c r="F45" s="3">
         <v>221400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>133100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>142800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>143600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>212200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>112600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>111800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>120100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>99300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>109300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>103400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>108900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>88300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>113100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>111900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>95600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>84000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>70500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>76700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>73800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>190400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>73200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>85500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>76500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>124600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>144800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>135100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>122500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>79700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>100400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>89300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>83400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>126500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>119100</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3051800</v>
+      </c>
+      <c r="E46" s="3">
         <v>2760800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2603000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2733700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2767200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2775500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2824700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3118700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2899600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2665900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2528100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2432600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2411600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2272800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2128800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2061800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2042100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2573500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2522500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2643000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2517100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2774500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2025800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2272200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2127200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1924600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1836100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1998600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2018100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1960200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1934700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2024500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1789300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1787400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1928200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1696900</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E47" s="3">
         <v>9300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>143200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>12000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>12400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>150700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>382500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>405800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>399500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>387600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>375000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>325500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>322200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>297200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>292600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>281800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>289800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>280300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>279800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>257300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>269600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>262200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>256200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>256800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>244800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>240500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>239100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>159100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>155000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>152400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>146300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>175100</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1082100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1059000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1054300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1034000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1079000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1097300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1121000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>797100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>809200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>804700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>805900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>756100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>766000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>780300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>787100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>766600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>777500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>716000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>693800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>675400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>680800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>703300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>728600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>711600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>721200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>724900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>554100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>487400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>490100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>492400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>493300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>495000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>492500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>482900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>473200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>478600</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10604300</v>
+      </c>
+      <c r="E49" s="3">
         <v>10548000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10471100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10501300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10466600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10519300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10612900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8762900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8728900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8751600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8714600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8444400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8407900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8531300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8607400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8525900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8613500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6993300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6848600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6833200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6823500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6843800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6810400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5978600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5951700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5979800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>6015800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5365200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5399400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5365300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5129000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5104700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5098200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4876000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4553000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>4626400</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,41 +5199,44 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>518500</v>
+      </c>
+      <c r="E52" s="3">
         <v>499900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>281400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>487800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>470900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>460500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>239900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>403700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>391700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>383400</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -5192,8 +5312,11 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15266500</v>
+      </c>
+      <c r="E54" s="3">
         <v>14877100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14631200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14767600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14795900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14865000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15023500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13093400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12839900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12616000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12431100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12038900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11985000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11972000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11898200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11679700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11755300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10579900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10357500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10433400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10311200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10601900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9844600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9219700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9069600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8891500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8662300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8108000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8152500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>8058400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7796100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7783300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7535000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>7298800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>7100700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>6977100</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,668 +5622,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>549300</v>
+      </c>
+      <c r="E57" s="3">
         <v>534400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>523300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>511700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>510500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>517400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>516600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>486600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>487700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>526100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>497100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>524300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>540700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>504200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>470300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>446400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>446500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>397100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>360400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>324800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>337500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>373900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>377200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>381900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>390400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>405600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>399600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>389100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>394300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>382300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>437300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>409400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>405900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>382800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>369500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>345500</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>463600</v>
+      </c>
+      <c r="E58" s="3">
         <v>527900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>709100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>625400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>886700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1115500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1479000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>349400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>51600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>116500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>226100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>272000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>354800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>331400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>315100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>415700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>700000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>94700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>132300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>505000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>115900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>510800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>497400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>199500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>98400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>104200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>358900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>68700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>307700</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>308100</v>
       </c>
       <c r="AG58" s="3">
         <v>308100</v>
       </c>
       <c r="AH58" s="3">
+        <v>308100</v>
+      </c>
+      <c r="AI58" s="3">
         <v>509600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>272600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>338000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>278900</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>613700</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>499200</v>
+      </c>
+      <c r="E59" s="3">
         <v>550000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>663600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>519800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>461800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>513900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>658600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>456100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>459600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>511800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>841000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>795100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>737600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>755100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>778000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>771800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>711100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>646700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>583300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>573600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>564100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>593000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>551200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>529000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>489800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>497400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>500300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>512000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>480600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>469500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>393200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>351400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>316700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>296000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>276000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>257600</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1868400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1962600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2098600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1966900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2203000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2502500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2882600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1673700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1341200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1452700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1564200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1591400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1633000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1590700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1563300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1633800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1857600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1138500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1075900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1403500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1017500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1477700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1425900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1110500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>978600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1007200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1258700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>969900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1182500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1159900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1138700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1270300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>995100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1016800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>924400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1216700</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1735100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1641700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1615400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1931900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1996000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2051600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2077900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1980600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2315900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2300900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2158900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2085400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2147400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2204600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2229100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2238900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2262100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2256900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2281400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2295800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2753300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2741800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2271300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2229300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2368700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2368200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2273800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1832500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1838200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1897600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1866200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1920900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2128800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2076600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2062600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>426000</v>
+      </c>
+      <c r="E62" s="3">
         <v>418600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>393800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>480700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>477800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>458600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>438900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>407600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>387600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>380300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1231500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1229500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1254500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1245000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1233800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1248600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1292200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1063800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1050800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1029900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1054000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1056500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1031900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1014000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1055600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1059400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>887800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>793700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>793600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>796400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>763600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>825900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>818800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>801200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>857100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>846400</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4877900</v>
+      </c>
+      <c r="E66" s="3">
         <v>4907200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4975900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5217400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5543500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5896800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6293300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4750900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4758500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4858900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4954600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4906300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5034900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5040300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5026300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5121300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5412000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4459100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4408100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4729200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4824700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5275900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4729100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4353700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4402800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4434900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4420400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3596100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3814400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3854000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3768400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4017100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3942800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3894600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3844200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>3603900</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11624800</v>
+      </c>
+      <c r="E72" s="3">
         <v>11338000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11057700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10735100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10459600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10186600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9940300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9655100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9372400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9105700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8857500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8600900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8353700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8121800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7900100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7664700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7453400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7267900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7094700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6915000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6751700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6626700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6387600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6198800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6010000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5826300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5653800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5474100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5315200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5153700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5002400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4784600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4651800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4522000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4403700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4315100</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10388700</v>
+      </c>
+      <c r="E76" s="3">
         <v>9969900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9655300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9550200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9252400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8968200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8730200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8342500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8081400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7757100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7476500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7132700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6950100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6931700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6871900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6558400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6343300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6120700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5949300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5704200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5486400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5326000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5115500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4866000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4666800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4456600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4241900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4511900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4338100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4204400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4027600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3766200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3592200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3404200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3256500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3373200</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>358400</v>
+      </c>
+      <c r="E81" s="3">
         <v>351800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>387300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>340200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>337700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>310900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>342900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>340400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>324200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>305700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>307100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>297600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>282400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>272400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>281700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>257500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>231700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>219200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>221000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>204600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>166200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>280600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>220800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>220700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>215500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>204300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>211500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>191200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>193900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>181300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>238500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>153500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>150500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>138900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>109100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>98000</v>
+        <v>35900</v>
       </c>
       <c r="E83" s="3">
+        <v>35300</v>
+      </c>
+      <c r="F83" s="3">
         <v>91900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>81800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>81600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>82400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>88500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>75800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>77100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>78100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>88500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>75800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>77100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>78100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>77600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>74700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>75200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>64600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>64900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>63000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>61300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>66100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>64100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>55300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>57200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>57500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>53600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>48100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>48900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>48800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>52200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>44600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>43800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>42500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>56700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>359100</v>
+      </c>
+      <c r="E89" s="3">
         <v>417500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>550000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>487200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>381400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>410200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>540700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>472900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>335200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>386500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>385000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>327100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>235900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>201300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>281900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>307100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>287000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>284400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>385900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>309700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>314600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>270800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>342200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>329600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>246300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>196300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>296200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>248800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>203100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>177400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>252900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>239000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>199000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>142400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>247300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>169000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-29300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-23100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-51700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-26300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-21400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-27700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-59700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-28700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-58200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-28300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-26200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-26400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-43400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-26200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-23500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-17500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-37000</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-10100</v>
       </c>
       <c r="W91" s="3">
         <v>-10100</v>
       </c>
       <c r="X91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-16900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-40800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-21900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-21400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-34600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-16300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-29400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-13400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-125700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-175300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-26000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-22100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2050100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-176300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-122200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-297200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-214500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-26200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-160700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-13000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1597600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-284500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-37100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-10800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>115600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-977600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-133700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-21900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-17800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-785800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-22500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-148200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-253600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-63400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-15700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-198400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-348300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-52400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-81800</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9296,7 +9530,7 @@
         <v>71500</v>
       </c>
       <c r="E96" s="3">
-        <v>64700</v>
+        <v>71500</v>
       </c>
       <c r="F96" s="3">
         <v>64700</v>
@@ -9308,7 +9542,7 @@
         <v>64700</v>
       </c>
       <c r="I96" s="3">
-        <v>57600</v>
+        <v>64700</v>
       </c>
       <c r="J96" s="3">
         <v>57600</v>
@@ -9317,70 +9551,70 @@
         <v>57600</v>
       </c>
       <c r="L96" s="3">
+        <v>57600</v>
+      </c>
+      <c r="M96" s="3">
         <v>57500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-50500</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-50400</v>
       </c>
       <c r="O96" s="3">
         <v>-50400</v>
       </c>
       <c r="P96" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-50800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-46300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-46200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-46100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-46000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-41300</v>
       </c>
       <c r="V96" s="3">
         <v>-41300</v>
       </c>
       <c r="W96" s="3">
-        <v>-41200</v>
+        <v>-41300</v>
       </c>
       <c r="X96" s="3">
         <v>-41200</v>
       </c>
       <c r="Y96" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-32000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-31800</v>
       </c>
       <c r="AB96" s="3">
         <v>-31800</v>
       </c>
       <c r="AC96" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-32400</v>
       </c>
       <c r="AE96" s="3">
         <v>-32400</v>
       </c>
       <c r="AF96" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-32300</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-20700</v>
       </c>
       <c r="AH96" s="3">
         <v>-20700</v>
@@ -9389,16 +9623,19 @@
         <v>-20700</v>
       </c>
       <c r="AJ96" s="3">
-        <v>-20600</v>
+        <v>-20700</v>
       </c>
       <c r="AK96" s="3">
         <v>-20600</v>
       </c>
       <c r="AL96" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-20700</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-131700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-277700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-374000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-476800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-334100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-417500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1062100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-47700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-102100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-215000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-74500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-130800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-183000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-187400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-131900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-320400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>575600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-84000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-454700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-141100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-430300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>486600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>280800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-16400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-25700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-165900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>330300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-261700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-28500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-27100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-286200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-75100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>51900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>98400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-97900</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>15300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-12500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>5100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>22200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-20500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-18400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>22200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-20500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-18400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>13900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>11300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>12200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-25600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>13700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>6600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>16500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>20800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>6900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-21600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>220700</v>
+      </c>
+      <c r="E102" s="3">
         <v>25000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-22300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>22800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-36000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-432100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>236300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>205700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>54500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>35400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-38700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-11900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-32000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-733000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-89200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-92000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>173900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-122400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>860400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-342300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>167500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>199800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>14100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-164700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-39000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-89500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-90100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>219900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-53800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-147000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>271800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-10700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>AME</t>
   </si>
@@ -656,518 +656,530 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1998400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1892600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1778100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1732000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1761600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1708600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1734800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1736200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1730900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1622800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1646100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1597100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1625700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1551800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1514600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1458500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1503700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1440700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1386300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1215700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1198900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1126900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1011900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1202200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1304800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1276600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1289400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1287700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1271300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1193000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1208900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1172600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1143100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1084800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1064600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1007700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>973000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1260500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1198700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1142200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1107000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1116900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1092800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1110400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1115500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1115900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1020900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1053200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1022500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1063700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1004600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>988200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>948800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>982400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>949400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>912700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>789400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>770000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>732700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>669200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>780900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>858200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>823300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>838200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>851300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>835300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>783000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>791200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>776800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>767000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>722100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>702200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>667400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>735600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>612700</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>737900</v>
+      </c>
+      <c r="E10" s="3">
         <v>693900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>635900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>625000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>644700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>615800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>624400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>620700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>615000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>601900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>592900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>574600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>562000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>547200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>526400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>509700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>521300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>491300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>473600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>426300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>428900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>394200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>342700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>421300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>446600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>453300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>451200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>436400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>436000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>410000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>417700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>395800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>376100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>362700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>362400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>340300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>237400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>332300</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,37 +1220,38 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E12" s="3">
         <v>94700</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
-        <v>371900</v>
+      <c r="G12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H12" s="3">
+        <v>181500</v>
+      </c>
+      <c r="I12" s="3">
         <v>94300</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>351700</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1324,8 +1337,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,16 +1456,19 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E14" s="3">
         <v>19800</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1457,17 +1476,17 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>29200</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1484,8 +1503,8 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1493,8 +1512,8 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1502,20 +1521,20 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>-97100</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1532,8 +1551,8 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1556,47 +1575,50 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>105700</v>
+      </c>
+      <c r="E15" s="3">
         <v>103100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>107700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>106400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>95900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>90400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>98700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>98000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>91900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>81800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>81600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>82400</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1648,8 +1670,8 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>8</v>
+      <c r="AG15" s="3">
+        <v>0</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>8</v>
@@ -1669,11 +1691,14 @@
       <c r="AM15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AN15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO15" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1736,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1448400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1404600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1325000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1287600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1263900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1270400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1296300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1301700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1253400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1194000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1237200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1205000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1227600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1167300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1149700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1105300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1142600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1103100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1069700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>922400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>900800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>856200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>784900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>829200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1007200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>975600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>994000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1004400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>989300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>927700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>938800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>914500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>913500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>854800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>835100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>790200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>799700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>743900</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>550000</v>
+      </c>
+      <c r="E18" s="3">
         <v>488100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>453100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>444400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>497700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>438100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>438600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>434400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>477500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>428900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>408900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>392100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>398100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>384500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>364900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>353200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>361100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>337600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>316600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>293300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>298100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>270700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>227000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>373000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>297600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>301000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>295400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>283300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>282000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>265300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>270100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>258100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>229600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>230000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>229500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>217500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>173300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>201100</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,588 +2017,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-5900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-8800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>38100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-11300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>48500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-6200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4400</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-1900</v>
       </c>
       <c r="W20" s="3">
         <v>-1900</v>
       </c>
       <c r="X20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>-1000</v>
       </c>
       <c r="AG20" s="3">
         <v>-1000</v>
       </c>
       <c r="AH20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-7800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-4400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>613300</v>
+      </c>
+      <c r="E21" s="3">
         <v>593400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>566700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>559600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>555400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>534300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>546300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>543800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>521000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>513700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>496700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>482500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>490000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>463500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>443900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>433900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>437400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>414800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>387400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>356000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>361000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>332300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>290500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>439900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>355100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>350800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>349200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>337100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>332700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>312500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>317900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>306300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>274000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>273800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>271800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>258500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>225600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E22" s="3">
         <v>22500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>16900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>19000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>25100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>30600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>35300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>24100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>18400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>23000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>20200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>20400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>19600</v>
-      </c>
-      <c r="S22" s="3">
-        <v>20500</v>
       </c>
       <c r="T22" s="3">
         <v>20500</v>
       </c>
       <c r="U22" s="3">
+        <v>20500</v>
+      </c>
+      <c r="V22" s="3">
         <v>20400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>18900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>21200</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>22700</v>
       </c>
       <c r="Z22" s="3">
         <v>22700</v>
       </c>
       <c r="AA22" s="3">
+        <v>22700</v>
+      </c>
+      <c r="AB22" s="3">
         <v>23000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>21300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>21500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>22700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>20300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>19400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>20800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>21700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>24300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>24700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>24600</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>24500</v>
-      </c>
-      <c r="AM22" s="3">
-        <v>23600</v>
       </c>
       <c r="AN22" s="3">
         <v>23600</v>
       </c>
+      <c r="AO22" s="3">
+        <v>23600</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>474000</v>
+      </c>
+      <c r="E23" s="3">
         <v>448000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>442200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>434200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>444400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>418800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>417000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>381300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>416900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>413500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>396400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>379600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>378500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>367500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>346500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>336200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>339300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>319700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>291800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>272500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>276700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>248100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>206500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>351100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>268000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>274200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>270600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>256900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>258800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>244900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>248200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>235800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>197500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>204400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>203400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>191400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>145300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>75400</v>
+      </c>
+      <c r="E24" s="3">
         <v>76500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>83800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>82500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>57100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>78600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>79300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>70400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>74100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>73100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>72100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>73900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>71400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>69900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>64100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>63800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>57600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>62200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>60100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>53200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>55700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>43500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>40200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>70500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>47200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>53500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>55100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>52700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>59100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>53700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>54400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>54500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>50600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>50900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>52900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>52500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>36100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2729,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>398600</v>
+      </c>
+      <c r="E26" s="3">
         <v>371400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>358400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>351800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>387300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>340200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>337700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>310900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>342900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>340400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>324200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>305700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>307100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>297600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>282400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>272400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>281700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>257500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>231700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>219200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>221000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>204600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>166200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>280600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>220800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>220700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>215500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>204300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>199700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>191200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>193900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>181300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>146900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>153500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>150500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>138900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>109100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>398600</v>
+      </c>
+      <c r="E27" s="3">
         <v>371400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>358400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>351800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>387300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>340200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>337700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>310900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>342900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>340400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>324200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>305700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>307100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>297600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>282400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>272400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>281700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>257500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>231700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>219200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>221000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>204600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>166200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>280600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>220800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>220700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>215500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>204300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>199700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>191200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>193900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>181300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>146900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>153500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>150500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>138900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>109100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3097,8 +3157,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -3115,11 +3175,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>11800</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -3127,11 +3187,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>91600</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3145,8 +3205,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,240 +3443,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="E32" s="3">
         <v>2200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>5900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>8800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-38100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>11300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-48500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>6200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4400</v>
-      </c>
-      <c r="V32" s="3">
-        <v>1900</v>
       </c>
       <c r="W32" s="3">
         <v>1900</v>
       </c>
       <c r="X32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Y32" s="3">
         <v>1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>5500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>3700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2900</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>1000</v>
       </c>
       <c r="AG32" s="3">
         <v>1000</v>
       </c>
       <c r="AH32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI32" s="3">
         <v>600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>7800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>4400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>398600</v>
+      </c>
+      <c r="E33" s="3">
         <v>371400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>358400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>351800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>387300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>340200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>337700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>310900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>342900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>340400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>324200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>305700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>307100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>297600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>282400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>272400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>281700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>257500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>231700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>219200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>221000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>204600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>166200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>280600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>220800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>220700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>215500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>204300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>211500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>191200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>193900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>181300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>238500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>153500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>150500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>138900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>109100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3800,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>398600</v>
+      </c>
+      <c r="E35" s="3">
         <v>371400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>358400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>351800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>387300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>340200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>337700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>310900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>342900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>340400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>324200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>305700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>307100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>297600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>282400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>272400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>281700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>257500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>231700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>219200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>221000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>204600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>166200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>280600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>220800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>220700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>215500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>204300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>211500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>191200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>193900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>181300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>238500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>153500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>150500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>138900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>109100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4131,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>458000</v>
+      </c>
+      <c r="E41" s="3">
         <v>439200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>619700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>399000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>374000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>396300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>396600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>373800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>409800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>841900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>605600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>399900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>345400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>309900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>348700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>340300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>346800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>358700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>390600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1123700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1212800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1304800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1131000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1253400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>393000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>735400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>567900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>368100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>354000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>518700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>557700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>556800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>646300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>736400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>516500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>570200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>717300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>445500</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4278,820 +4367,844 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1172000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1309300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1181400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1154400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>985900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1119700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1126100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1130800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1070200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1076600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1074400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1028900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1039100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>988100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>993000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>957200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>924500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>851400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>827900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>749900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>666400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>682900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>688000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>793000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>817800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>840000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>839600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>839500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>732800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>714900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>711000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>684600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>668200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>640800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>642300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>603900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>592300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>595100</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1106400</v>
+      </c>
+      <c r="E44" s="3">
         <v>1153100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1110500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1069500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1021700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1084600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1101700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1127300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1132500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1087600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1107800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1117100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1044300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1025100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>966600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>866500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>769200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>738700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>711600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>604300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>559200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>584800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>621500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>654300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>624600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>623700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>634100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>640600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>624700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>620100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>614400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>596300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>540500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>546900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>541200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>529900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>492100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>537200</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>283500</v>
+      </c>
+      <c r="E45" s="3">
         <v>159900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>140200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>137900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>221400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>133100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>142800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>143600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>212200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>112600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>111800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>120100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>99300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>109300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>103400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>108900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>88300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>113100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>111900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>95600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>84000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>70500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>76700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>73800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>190400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>73200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>85500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>76500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>124600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>144800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>135100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>122500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>79700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>100400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>89300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>83400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>126500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>119100</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3019800</v>
+      </c>
+      <c r="E46" s="3">
         <v>3061500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3051800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2760800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2603000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2733700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2767200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2775500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2824700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3118700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2899600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2665900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2528100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2432600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2411600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2272800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2128800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2061800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2042100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2573500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2522500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2643000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2517100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2774500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2025800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2272200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2127200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1924600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1836100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1998600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2018100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1960200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1934700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2024500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1789300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1787400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1928200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1696900</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E47" s="3">
         <v>8000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9300</v>
       </c>
-      <c r="G47" s="3">
-        <v>143200</v>
-      </c>
       <c r="H47" s="3">
+        <v>9100</v>
+      </c>
+      <c r="I47" s="3">
         <v>10900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>12400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>150700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>382500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>405800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>399500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>387600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>375000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>325500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>322200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>297200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>292600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>281800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>289800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>280300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>279800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>257300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>269600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>262200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>256200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>256800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>244800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>240500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>239100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>159100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>155000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>152400</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>146300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>175100</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1128400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1113200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1082100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1059000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1054300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1034000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1079000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1097300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1121000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>797100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>809200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>804700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>805900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>756100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>766000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>780300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>787100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>766600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>777500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>716000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>693800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>675400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>680800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>703300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>728600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>711600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>721200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>724900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>554100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>487400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>490100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>492400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>493300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>495000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>492500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>482900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>473200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>478600</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11299200</v>
+      </c>
+      <c r="E49" s="3">
         <v>11431000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10604300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10548000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10471100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10501300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10466600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10519300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10612900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8762900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8728900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8751600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8714600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8444400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8407900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8531300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8607400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8525900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8613500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6993300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6848600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6833200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6823500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6843800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6810400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5978600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5951700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5979800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>6015800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5365200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5399400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5365300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5129000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5104700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5098200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>4876000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>4553000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>4626400</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,47 +5438,50 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>612000</v>
+      </c>
+      <c r="E52" s="3">
         <v>568500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>518500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>499900</v>
       </c>
-      <c r="G52" s="3">
-        <v>281400</v>
-      </c>
       <c r="H52" s="3">
+        <v>493700</v>
+      </c>
+      <c r="I52" s="3">
         <v>487800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>470900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>460500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>239900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>403700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>391700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>383400</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
@@ -5438,8 +5557,11 @@
       <c r="AN52" s="3">
         <v>0</v>
       </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16067500</v>
+      </c>
+      <c r="E54" s="3">
         <v>16182300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15266500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14877100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14631200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14767600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14795900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14865000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15023500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13093400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12839900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12616000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12431100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12038900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11985000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11972000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11898200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>11679700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>11755300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10579900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10357500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10433400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10311200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10601900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9844600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9219700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9069600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8891500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8662300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>8108000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>8152500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>8058400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7796100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>7783300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>7535000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>7298800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>7100700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>6977100</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,704 +5883,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>618000</v>
+      </c>
+      <c r="E57" s="3">
         <v>582000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>549300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>534400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>523300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>511700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>510500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>517400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>516600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>486600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>487700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>526100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>497100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>524300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>540700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>504200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>470300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>446400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>446500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>397100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>360400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>324800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>337500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>373900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>377200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>381900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>390400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>405600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>399600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>389100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>394300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>382300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>437300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>409400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>405900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>382800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>369500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>345500</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1270100</v>
+      </c>
+      <c r="E58" s="3">
         <v>1099400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>463600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>527900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>709100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>625400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>886700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1115500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1479000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>349400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>51600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>116500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>226100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>272000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>354800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>331400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>315100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>415700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>700000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>94700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>132300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>505000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>115900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>510800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>497400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>199500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>98400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>104200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>358900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>68700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>307700</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>308100</v>
       </c>
       <c r="AI58" s="3">
         <v>308100</v>
       </c>
       <c r="AJ58" s="3">
+        <v>308100</v>
+      </c>
+      <c r="AK58" s="3">
         <v>509600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>272600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>338000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>278900</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>613700</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>714800</v>
+      </c>
+      <c r="E59" s="3">
         <v>541400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>499200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>550000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>663600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>519800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>461800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>513900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>658600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>456100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>459600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>511800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>841000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>795100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>737600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>755100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>778000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>771800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>711100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>646700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>583300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>573600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>564100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>593000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>551200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>529000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>489800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>497400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>500300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>512000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>480600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>469500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>393200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>351400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>316700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>296000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>276000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>257600</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2842800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2649800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1868400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1962600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2098600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1966900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2203000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2502500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2882600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1673700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1341200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1452700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1564200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1591400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1633000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1590700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1563300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1633800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1857600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1138500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1075900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1403500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1017500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1477700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1425900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1110500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>978600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1007200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1258700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>969900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1182500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1159900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1138700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1270300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>995100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1016800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>924400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1216700</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1301400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1647000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1735100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1641700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1615400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1931900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1996000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2051600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2077900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1980600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2315900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2300900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2158900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2085400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2147400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2204600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2229100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2238900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2262100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2256900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2281400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2295800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2753300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2741800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2271300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2229300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2368700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2368200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2273800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1832500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1838200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1897600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1866200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1920900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2128800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2076600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2062600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>453000</v>
+      </c>
+      <c r="E62" s="3">
         <v>456600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>426000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>418600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>393800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>480700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>477800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>458600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>438900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>407600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>387600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>380300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1231500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1229500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1254500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1245000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1233800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1248600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1292200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1063800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1050800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1029900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1054000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1056500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1031900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1014000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1055600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1059400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>887800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>793700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>793600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>796400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>763600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>825900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>818800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>801200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>857100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>846400</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5438800</v>
+      </c>
+      <c r="E66" s="3">
         <v>5655400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4877900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4907200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4975900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5217400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5543500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5896800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6293300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4750900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4758500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4858900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4954600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4906300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5034900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5040300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5026300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5121300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5412000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4459100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4408100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4729200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4824700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5275900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4729100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4353700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4402800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4434900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4420400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3596100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3814400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3854000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3768400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4017100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3942800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>3894600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>3844200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>3603900</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12252500</v>
+      </c>
+      <c r="E72" s="3">
         <v>11924900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11624800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11338000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11057700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10735100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10459600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10186600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9940300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9655100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9372400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9105700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8857500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8600900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8353700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8121800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7900100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7664700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7453400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7267900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7094700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6915000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6751700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6626700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6387600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6198800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6010000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5826300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5653800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5474100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5315200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5153700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5002400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4784600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4651800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4522000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4403700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4315100</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10628800</v>
+      </c>
+      <c r="E76" s="3">
         <v>10526900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10388700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9969900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9655300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9550200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9252400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8968200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8730200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8342500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8081400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7757100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7476500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7132700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6950100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6931700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6871900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6558400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6343300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6120700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5949300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5704200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5486400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5326000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5115500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4866000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4666800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4456600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4241900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4511900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4338100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4204400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4027600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3766200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3592200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3404200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3256500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3373200</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8304,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>398600</v>
+      </c>
+      <c r="E81" s="3">
         <v>371400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>358400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>351800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>387300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>340200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>337700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>310900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>342900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>340400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>324200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>305700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>307100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>297600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>282400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>272400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>281700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>257500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>231700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>219200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>221000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>204600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>166200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>280600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>220800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>220700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>215500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>204300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>211500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>191200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>193900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>181300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>238500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>153500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>150500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>138900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>109100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8592,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E83" s="3">
         <v>30500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>35900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>35300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>91900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>81800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>81600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>82400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>88500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>75800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>77100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>78100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>88500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>75800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>77100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>78100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>77600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>74700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>75200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>64600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>64900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>63000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>61300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>66100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>64100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>55300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>57200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>57500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>53600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>48100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>48900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>48800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>52200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>44600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>43800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>42500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>56700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>584300</v>
+      </c>
+      <c r="E89" s="3">
         <v>440900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>359100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>417500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>550000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>487200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>381400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>410200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>540700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>472900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>335200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>386500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>385000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>327100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>235900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>201300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>281900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>307100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>287000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>284400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>385900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>309700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>314600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>270800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>342200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>329600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>246300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>196300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>296200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>248800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>203100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>177400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>252900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>239000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>199000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>142400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>247300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>169000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9468,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-20900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-29300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-23100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-51700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-26300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-21400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-27700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-59700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-28700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-27800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-20000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-58200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-26200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-26400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-43400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-26200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-23500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-17500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-37000</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-10100</v>
       </c>
       <c r="Y91" s="3">
         <v>-10100</v>
       </c>
       <c r="Z91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-16900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-40800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-21900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-21400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-34600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-16300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-12300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-29400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-13400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9823,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-850000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-30000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-125700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-175300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-26000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-22100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-21400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2050100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-176300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-27800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-122200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-297200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-214500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-26200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-14900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-160700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1597600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-284500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-37100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>115600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-977600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-133700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-21900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-17800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-785800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-22500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-148200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-253600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-63400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-15700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-198400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-348300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-52400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-81800</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,22 +9987,23 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E96" s="3">
         <v>71400</v>
-      </c>
-      <c r="E96" s="3">
-        <v>71500</v>
       </c>
       <c r="F96" s="3">
         <v>71500</v>
       </c>
       <c r="G96" s="3">
-        <v>64700</v>
+        <v>71500</v>
       </c>
       <c r="H96" s="3">
         <v>64700</v>
@@ -9782,7 +10015,7 @@
         <v>64700</v>
       </c>
       <c r="K96" s="3">
-        <v>57600</v>
+        <v>64700</v>
       </c>
       <c r="L96" s="3">
         <v>57600</v>
@@ -9791,70 +10024,70 @@
         <v>57600</v>
       </c>
       <c r="N96" s="3">
+        <v>57600</v>
+      </c>
+      <c r="O96" s="3">
         <v>57500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-50500</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-50400</v>
       </c>
       <c r="Q96" s="3">
         <v>-50400</v>
       </c>
       <c r="R96" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="S96" s="3">
         <v>-50800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-46300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-46200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-46100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-46000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-41300</v>
       </c>
       <c r="X96" s="3">
         <v>-41300</v>
       </c>
       <c r="Y96" s="3">
-        <v>-41200</v>
+        <v>-41300</v>
       </c>
       <c r="Z96" s="3">
         <v>-41200</v>
       </c>
       <c r="AA96" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-32000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-31800</v>
       </c>
       <c r="AD96" s="3">
         <v>-31800</v>
       </c>
       <c r="AE96" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-32400</v>
       </c>
       <c r="AG96" s="3">
         <v>-32400</v>
       </c>
       <c r="AH96" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-32300</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-20700</v>
       </c>
       <c r="AJ96" s="3">
         <v>-20700</v>
@@ -9863,16 +10096,19 @@
         <v>-20700</v>
       </c>
       <c r="AL96" s="3">
-        <v>-20600</v>
+        <v>-20700</v>
       </c>
       <c r="AM96" s="3">
         <v>-20600</v>
       </c>
       <c r="AN96" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-20700</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10461,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-509700</v>
+      </c>
+      <c r="E100" s="3">
         <v>232700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-131700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-277700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-374000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-476800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-334100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-417500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1062100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-47700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-102100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-215000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-74500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-130800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-183000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-187400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-131900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-320400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>575600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-84000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-454700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-141100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-430300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>486600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>280800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-16400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-25700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-165900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>330300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-261700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-28500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-27100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-286200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-75100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>51900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>98400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-97900</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E101" s="3">
         <v>15300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>15300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-12500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>5100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>22200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-20500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-18400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>22200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-18400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-5100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>13900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>11300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>4000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>12200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-25600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>13700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>16500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>20800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>6900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-21600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-180500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>220700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>25000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-22300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>22800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-36000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-432100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>236300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>205700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>54500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>35400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-38700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-32000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-733000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-89200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-92000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>173900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-122400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>860400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-342300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>167500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>199800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>14100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-164700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-39000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-89500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-90100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>219900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-53800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-147000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>271800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-10700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>AME</t>
   </si>
@@ -656,530 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1928400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1998400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1892600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1778100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1732000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1761600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1708600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1734800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1736200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1730900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1622800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1646100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1597100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1625700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1551800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1514600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1458500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1503700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1440700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1386300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1215700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1198900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1126900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1011900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1202200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1304800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1276600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1289400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1287700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1271300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1193000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1208900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1172600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1143100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1084800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1064600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1007700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>973000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>945000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1209300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1260500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1198700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1142200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1107000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1116900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1092800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1110400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1115500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1115900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1020900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1053200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1022500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1063700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1004600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>988200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>948800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>982400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>949400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>912700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>789400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>770000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>732700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>669200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>780900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>858200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>823300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>838200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>851300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>835300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>783000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>791200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>776800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>767000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>722100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>702200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>667400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>735600</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>612700</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>719200</v>
+      </c>
+      <c r="E10" s="3">
         <v>737900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>693900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>635900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>625000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>644700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>615800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>624400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>620700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>615000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>601900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>592900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>574600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>562000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>547200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>526400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>509700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>521300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>491300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>473600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>426300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>428900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>394200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>342700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>421300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>446600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>453300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>451200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>436400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>436000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>410000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>417700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>395800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>376100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>362700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>362400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>340300</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>237400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>332300</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,40 +1234,41 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>111600</v>
+      </c>
+      <c r="E12" s="3">
         <v>99000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>94700</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H12" s="3">
+        <v>94900</v>
+      </c>
+      <c r="I12" s="3">
         <v>181500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>94300</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>351700</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,37 +1476,40 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E14" s="3">
         <v>17500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>19800</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>29200</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1506,8 +1526,8 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1515,8 +1535,8 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1524,20 +1544,20 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
+      <c r="X14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-97100</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1554,8 +1574,8 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1578,50 +1598,53 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>105500</v>
+      </c>
+      <c r="E15" s="3">
         <v>105700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>103100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>107700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>106400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>95900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>90400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>98700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>98000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>91900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>81800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>81600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>82400</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1673,8 +1696,8 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>8</v>
+      <c r="AH15" s="3">
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="s">
         <v>8</v>
@@ -1694,11 +1717,14 @@
       <c r="AN15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AO15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP15" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1421300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1448400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1404600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1325000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1287600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1263900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1270400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1296300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1301700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1253400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1194000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1237200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1205000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1227600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1167300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1149700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1105300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1142600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1103100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1069700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>922400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>900800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>856200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>784900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>829200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1007200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>975600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>994000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1004400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>989300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>927700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>938800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>914500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>913500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>854800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>835100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>790200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>799700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>743900</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>507200</v>
+      </c>
+      <c r="E18" s="3">
         <v>550000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>488100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>453100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>444400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>497700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>438100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>438600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>434400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>477500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>428900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>408900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>392100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>398100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>384500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>364900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>353200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>361100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>337600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>316600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>293300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>298100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>270700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>227000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>373000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>297600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>301000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>295400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>283300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>282000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>265300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>270100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>258100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>229600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>230000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>229500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>217500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>173300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>201100</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,603 +2051,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E20" s="3">
         <v>42400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>38100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-11300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>48500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-8000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4400</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-1900</v>
       </c>
       <c r="X20" s="3">
         <v>-1900</v>
       </c>
       <c r="Y20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2900</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-1000</v>
       </c>
       <c r="AH20" s="3">
         <v>-1000</v>
       </c>
       <c r="AI20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-7800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-4400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>621000</v>
+      </c>
+      <c r="E21" s="3">
         <v>613300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>593400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>566700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>559600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>555400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>534300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>546300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>543800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>521000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>513700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>496700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>482500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>490000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>463500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>443900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>433900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>437400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>414800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>387400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>356000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>361000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>332300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>290500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>439900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>355100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>350800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>349200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>337100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>332700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>312500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>317900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>306300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>274000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>273800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>271800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>258500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>225600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>239900</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E22" s="3">
         <v>22900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>22500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>16900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>19000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>22000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>25100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>30600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>35300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>24100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>18700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>23000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>20200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>20400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>19600</v>
-      </c>
-      <c r="T22" s="3">
-        <v>20500</v>
       </c>
       <c r="U22" s="3">
         <v>20500</v>
       </c>
       <c r="V22" s="3">
+        <v>20500</v>
+      </c>
+      <c r="W22" s="3">
         <v>20400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>18900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>19500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>21200</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>22700</v>
       </c>
       <c r="AA22" s="3">
         <v>22700</v>
       </c>
       <c r="AB22" s="3">
+        <v>22700</v>
+      </c>
+      <c r="AC22" s="3">
         <v>23000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>21300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>21500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>22700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>20300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>19400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>20800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>21700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>24300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>24700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>24600</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>24500</v>
-      </c>
-      <c r="AN22" s="3">
-        <v>23600</v>
       </c>
       <c r="AO22" s="3">
         <v>23600</v>
       </c>
+      <c r="AP22" s="3">
+        <v>23600</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>493000</v>
+      </c>
+      <c r="E23" s="3">
         <v>474000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>448000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>442200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>434200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>444400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>418800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>417000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>381300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>416900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>413500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>396400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>379600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>378500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>367500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>346500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>336200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>339300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>319700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>291800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>272500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>276700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>248100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>206500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>351100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>268000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>274200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>270600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>256900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>258800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>244900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>248200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>235800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>197500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>204400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>203400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>191400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>145300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>174200</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E24" s="3">
         <v>75400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>76500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>83800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>82500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>57100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>78600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>79300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>70400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>74100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>73100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>72100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>73900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>71400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>69900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>64100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>63800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>57600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>62200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>60100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>53200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>55700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>43500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>40200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>70500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>47200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>53500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>55100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>52700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>59100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>53700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>54400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>54500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>50600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>50900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>52900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>52500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>36100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>43600</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>399400</v>
+      </c>
+      <c r="E26" s="3">
         <v>398600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>371400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>358400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>351800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>387300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>340200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>337700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>310900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>342900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>340400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>324200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>305700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>307100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>297600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>282400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>272400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>281700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>257500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>231700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>219200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>221000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>204600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>166200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>280600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>220800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>220700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>215500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>204300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>199700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>191200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>193900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>181300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>146900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>153500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>150500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>138900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>109100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>399400</v>
+      </c>
+      <c r="E27" s="3">
         <v>398600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>371400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>358400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>351800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>387300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>340200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>337700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>310900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>342900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>340400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>324200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>305700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>307100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>297600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>282400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>272400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>281700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>257500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>231700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>219200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>221000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>204600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>166200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>280600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>220800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>220700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>215500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>204300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>199700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>191200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>193900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>181300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>146900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>153500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>150500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>138900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>109100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3160,8 +3221,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3178,11 +3239,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>11800</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -3190,11 +3251,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>91600</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3208,8 +3269,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,246 +3513,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-42400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-38100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>11300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-48500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>8000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4400</v>
-      </c>
-      <c r="W32" s="3">
-        <v>1900</v>
       </c>
       <c r="X32" s="3">
         <v>1900</v>
       </c>
       <c r="Y32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>6600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>5500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>3300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>3700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2900</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>1000</v>
       </c>
       <c r="AH32" s="3">
         <v>1000</v>
       </c>
       <c r="AI32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>7800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>1500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>4400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>399400</v>
+      </c>
+      <c r="E33" s="3">
         <v>398600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>371400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>358400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>351800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>387300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>340200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>337700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>310900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>342900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>340400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>324200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>305700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>307100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>297600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>282400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>272400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>281700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>257500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>231700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>219200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>221000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>204600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>166200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>280600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>220800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>220700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>215500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>204300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>211500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>191200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>193900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>181300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>238500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>153500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>150500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>138900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>109100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>399400</v>
+      </c>
+      <c r="E35" s="3">
         <v>398600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>371400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>358400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>351800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>387300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>340200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>337700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>310900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>342900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>340400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>324200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>305700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>307100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>297600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>282400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>272400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>281700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>257500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>231700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>219200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>221000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>204600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>166200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>280600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>220800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>220700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>215500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>204300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>211500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>191200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>193900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>181300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>238500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>153500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>150500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>138900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>109100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,127 +4218,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>481300</v>
+      </c>
+      <c r="E41" s="3">
         <v>458000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>439200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>619700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>399000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>374000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>396300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>396600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>373800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>409800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>841900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>605600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>399900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>345400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>309900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>348700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>340300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>346800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>358700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>390600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1123700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1212800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1304800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1131000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1253400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>393000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>735400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>567900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>368100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>354000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>518700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>557700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>556800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>646300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>736400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>516500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>570200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>717300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>445500</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4370,484 +4460,499 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1195800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1172000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1309300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1181400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1154400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>985900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1119700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1126100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1130800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1070200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1076600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1074400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1028900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1039100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>988100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>993000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>957200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>924500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>851400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>827900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>749900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>666400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>682900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>688000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>793000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>817800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>840000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>839600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>839500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>732800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>714900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>711000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>684600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>668200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>640800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>642300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>603900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>592300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>595100</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1143400</v>
+      </c>
+      <c r="E44" s="3">
         <v>1106400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1153100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1110500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1069500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1021700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1084600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1101700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1127300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1132500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1087600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1107800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1117100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1044300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1025100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>966600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>866500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>769200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>738700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>711600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>604300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>559200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>584800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>621500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>654300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>624600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>623700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>634100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>640600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>624700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>620100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>614400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>596300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>540500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>546900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>541200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>529900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>492100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>537200</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>317100</v>
+      </c>
+      <c r="E45" s="3">
         <v>283500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>159900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>140200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>137900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>221400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>133100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>142800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>143600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>212200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>112600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>111800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>120100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>99300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>109300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>103400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>108900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>88300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>113100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>111900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>95600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>84000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>70500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>76700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>73800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>190400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>73200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>85500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>76500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>124600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>144800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>135100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>122500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>79700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>100400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>89300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>83400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>126500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>119100</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3137500</v>
+      </c>
+      <c r="E46" s="3">
         <v>3019800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3061500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3051800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2760800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2603000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2733700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2767200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2775500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2824700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3118700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2899600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2665900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2528100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2432600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2411600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2272800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2128800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2061800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2042100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2573500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2522500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2643000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2517100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2774500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2025800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2272200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2127200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1924600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1836100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1998600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2018100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1960200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1934700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2024500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1789300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1787400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1928200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1696900</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4855,356 +4960,365 @@
         <v>8200</v>
       </c>
       <c r="E47" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F47" s="3">
         <v>8000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>12000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>150700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>382500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>405800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>399500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>387600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>375000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>325500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>322200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>297200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>292600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>281800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>289800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>280300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>279800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>257300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>269600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>262200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>256200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>256800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>244800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>240500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>239100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>159100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>155000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>152400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>146300</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>175100</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1103600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1128400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1113200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1082100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1059000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1054300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1034000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1079000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1097300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1121000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>797100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>809200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>804700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>805900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>756100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>766000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>780300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>787100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>766600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>777500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>716000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>693800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>675400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>680800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>703300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>728600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>711600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>721200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>724900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>554100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>487400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>490100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>492400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>493300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>495000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>492500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>482900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>473200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>478600</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11431400</v>
+      </c>
+      <c r="E49" s="3">
         <v>11299200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11431000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10604300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10548000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10471100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10501300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10466600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10519300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10612900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8762900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8728900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8751600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8714600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8444400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8407900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8531300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8607400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8525900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8613500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6993300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6848600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6833200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6823500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6843800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>6810400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5978600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5951700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5979800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6015800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5365200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5399400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5365300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5129000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5104700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5098200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>4876000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>4553000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>4626400</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,50 +5558,53 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>628800</v>
+      </c>
+      <c r="E52" s="3">
         <v>612000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>568500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>518500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>499900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>493700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>487800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>470900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>460500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>239900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>403700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>391700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>383400</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
@@ -5560,8 +5680,11 @@
       <c r="AO52" s="3">
         <v>0</v>
       </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16309500</v>
+      </c>
+      <c r="E54" s="3">
         <v>16067500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16182300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15266500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14877100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14631200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14767600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14795900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14865000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15023500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13093400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12839900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12616000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12431100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12038900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11985000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11972000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>11898200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>11679700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11755300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10579900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10357500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10433400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10311200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10601900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9844600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9219700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9069600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8891500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>8662300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>8108000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>8152500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>8058400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>7796100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>7783300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>7535000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>7298800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>7100700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>6977100</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,722 +6014,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>619300</v>
+      </c>
+      <c r="E57" s="3">
         <v>618000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>582000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>549300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>534400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>523300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>511700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>510500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>517400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>516600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>486600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>487700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>526100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>497100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>524300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>540700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>504200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>470300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>446400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>446500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>397100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>360400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>324800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>337500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>373900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>377200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>381900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>390400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>405600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>399600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>389100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>394300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>382300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>437300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>409400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>405900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>382800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>369500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>345500</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1176000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1270100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1099400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>463600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>527900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>709100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>625400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>886700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1115500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1479000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>349400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>51600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>116500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>226100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>272000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>354800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>331400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>315100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>415700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>700000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>94700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>132300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>505000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>115900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>510800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>497400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>199500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>98400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>104200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>358900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>68700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>307700</v>
-      </c>
-      <c r="AI58" s="3">
-        <v>308100</v>
       </c>
       <c r="AJ58" s="3">
         <v>308100</v>
       </c>
       <c r="AK58" s="3">
+        <v>308100</v>
+      </c>
+      <c r="AL58" s="3">
         <v>509600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>272600</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>338000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>278900</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>613700</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>598300</v>
+      </c>
+      <c r="E59" s="3">
         <v>714800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>541400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>499200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>550000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>663600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>519800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>461800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>513900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>658600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>456100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>459600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>511800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>841000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>795100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>737600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>755100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>778000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>771800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>711100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>646700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>583300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>573600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>564100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>593000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>551200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>529000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>489800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>497400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>500300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>512000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>480600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>469500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>393200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>351400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>316700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>296000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>276000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>257600</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2756100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2842800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2649800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1868400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1962600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2098600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1966900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2203000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2502500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2882600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1673700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1341200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1452700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1564200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1591400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1633000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1590700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1563300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1633800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1857600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1138500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1075900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1403500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1017500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1477700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1425900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1110500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>978600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1007200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1258700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>969900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1182500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1159900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1138700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1270300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>995100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1016800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>924400</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1216700</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1279700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1301400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1647000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1735100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1641700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1615400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1931900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1996000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2051600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2077900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1980600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2315900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2300900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2158900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2085400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2147400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2204600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2229100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2238900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2262100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2256900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2281400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2295800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2753300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2741800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2271300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2229300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2368700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2368200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2273800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1832500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1838200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1897600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1866200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1920900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2128800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2076600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2062600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1540700</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>473900</v>
+      </c>
+      <c r="E62" s="3">
         <v>453000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>456600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>426000</v>
       </c>
-      <c r="G62" s="3">
-        <v>418600</v>
-      </c>
       <c r="H62" s="3">
+        <v>418700</v>
+      </c>
+      <c r="I62" s="3">
         <v>393800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>480700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>477800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>458600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>438900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>407600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>387600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>380300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1231500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1229500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1254500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1245000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1233800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1248600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1292200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1063800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1050800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1029900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1054000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1056500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1031900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1014000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1055600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1059400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>887800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>793700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>793600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>796400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>763600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>825900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>818800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>801200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>857100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>846400</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5390200</v>
+      </c>
+      <c r="E66" s="3">
         <v>5438800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5655400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4877900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4907200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4975900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5217400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5543500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5896800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6293300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4750900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4758500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4858900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4954600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4906300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5034900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5040300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5026300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5121300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5412000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4459100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4408100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4729200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4824700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5275900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4729100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4353700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4402800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4434900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4420400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3596100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3814400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3854000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3768400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4017100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>3942800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>3894600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>3844200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>3603900</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12574000</v>
+      </c>
+      <c r="E72" s="3">
         <v>12252500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11924900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11624800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11338000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11057700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10735100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10459600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10186600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9940300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9655100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9372400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9105700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8857500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8600900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8353700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8121800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7900100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7664700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7453400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7267900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7094700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6915000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6751700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6626700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6387600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6198800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6010000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5826300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5653800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5474100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5315200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5153700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5002400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4784600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4651800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4522000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4403700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4315100</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10919300</v>
+      </c>
+      <c r="E76" s="3">
         <v>10628800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10526900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10388700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9969900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9655300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9550200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9252400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8968200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8730200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8342500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8081400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7757100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7476500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7132700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6950100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6931700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6871900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6558400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6343300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6120700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5949300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5704200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5486400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5326000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5115500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4866000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4666800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4456600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4241900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4511900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4338100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4204400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4027600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3766200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3592200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3404200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3256500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3373200</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>399400</v>
+      </c>
+      <c r="E81" s="3">
         <v>398600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>371400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>358400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>351800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>387300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>340200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>337700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>310900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>342900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>340400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>324200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>305700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>307100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>297600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>282400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>272400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>281700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>257500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>231700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>219200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>221000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>204600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>166200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>280600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>220800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>220700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>215500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>204300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>211500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>191200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>193900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>181300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>238500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>153500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>150500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>138900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>109100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>130700</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,127 +8791,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>35600</v>
+      </c>
+      <c r="E83" s="3">
         <v>33600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>30500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>35900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>35300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>91900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>81800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>81600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>82400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>88500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>75800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>77100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>78100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>88500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>75800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>77100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>78100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>77600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>74700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>75200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>64600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>64900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>63000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>61300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>66100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>64100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>55300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>57200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>57500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>53600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>48100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>48900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>48800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>52200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>44600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>43800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>42500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>56700</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>42000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>451500</v>
+      </c>
+      <c r="E89" s="3">
         <v>584300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>440900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>359100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>417500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>550000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>487200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>381400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>410200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>540700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>472900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>335200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>386500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>385000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>327100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>235900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>201300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>281900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>307100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>287000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>284400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>385900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>309700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>314600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>270800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>342200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>329600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>246300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>196300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>296200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>248800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>203100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>177400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>252900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>239000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>199000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>142400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>247300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>169000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,127 +9689,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-57000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-29300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-23100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-51700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-26300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-21400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-59700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-28700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-27800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-20000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-58200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-28300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-26200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-26400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-43400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-26200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-23500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-17500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-37000</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-10100</v>
       </c>
       <c r="Z91" s="3">
         <v>-10100</v>
       </c>
       <c r="AA91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-16900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-40800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-21900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-21400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-34600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-18900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-16300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-12300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-29400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-13400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-15200</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10053,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-234600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-57000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-850000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-30000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-125700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-175300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-26000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-21400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2050100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-176300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-27800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-122200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-297200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-214500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-26200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-14900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-160700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-13000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1597600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-284500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-37100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>115600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-977600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-133700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-21900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-17800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-785800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-22500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-148200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-253600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-63400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-15700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-198400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-348300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-52400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-81800</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,25 +10221,26 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>77800</v>
+      </c>
+      <c r="E96" s="3">
         <v>71000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>71400</v>
-      </c>
-      <c r="F96" s="3">
-        <v>71500</v>
       </c>
       <c r="G96" s="3">
         <v>71500</v>
       </c>
       <c r="H96" s="3">
-        <v>64700</v>
+        <v>71500</v>
       </c>
       <c r="I96" s="3">
         <v>64700</v>
@@ -10018,7 +10252,7 @@
         <v>64700</v>
       </c>
       <c r="L96" s="3">
-        <v>57600</v>
+        <v>64700</v>
       </c>
       <c r="M96" s="3">
         <v>57600</v>
@@ -10027,70 +10261,70 @@
         <v>57600</v>
       </c>
       <c r="O96" s="3">
+        <v>57600</v>
+      </c>
+      <c r="P96" s="3">
         <v>57500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-50500</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-50400</v>
       </c>
       <c r="R96" s="3">
         <v>-50400</v>
       </c>
       <c r="S96" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="T96" s="3">
         <v>-50800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-46300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-46200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-46100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-46000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-41300</v>
       </c>
       <c r="Y96" s="3">
         <v>-41300</v>
       </c>
       <c r="Z96" s="3">
-        <v>-41200</v>
+        <v>-41300</v>
       </c>
       <c r="AA96" s="3">
         <v>-41200</v>
       </c>
       <c r="AB96" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-32000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-31800</v>
       </c>
       <c r="AE96" s="3">
         <v>-31800</v>
       </c>
       <c r="AF96" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-31900</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-32400</v>
       </c>
       <c r="AH96" s="3">
         <v>-32400</v>
       </c>
       <c r="AI96" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-32300</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-20700</v>
       </c>
       <c r="AK96" s="3">
         <v>-20700</v>
@@ -10099,16 +10333,19 @@
         <v>-20700</v>
       </c>
       <c r="AM96" s="3">
-        <v>-20600</v>
+        <v>-20700</v>
       </c>
       <c r="AN96" s="3">
         <v>-20600</v>
       </c>
       <c r="AO96" s="3">
+        <v>-20600</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-20700</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,361 +10707,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-188000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-509700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>232700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-131700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-277700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-374000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-476800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-334100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-417500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1062100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-47700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-102100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-215000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-74500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-130800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-183000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-187400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-131900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-320400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>575600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-84000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-454700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-141100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-430300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>486600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>280800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-16400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-25700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-165900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>330300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-261700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-28500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-27100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-286200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-19800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-75100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>51900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>98400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-97900</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-23000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>15300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-7300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>15300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-12500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>22200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-20500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-18400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>22200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-20500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-18400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-5500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-5600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-5100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>13900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>11300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>4000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-12600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>12200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-25600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>13700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>6600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>16500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>20800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>6900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-21600</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E102" s="3">
         <v>18700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-180500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>220700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>25000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-22300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>22800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-36000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-432100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>236300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>205700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>54500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>35400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-38700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-11900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-32000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-733000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-89200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-92000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>173900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-122400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>860400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-342300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>167500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>199800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>14100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-164700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-39000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-89500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-90100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>219900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-53800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-147000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>271800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-10700</v>
       </c>
     </row>
